--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -87,7 +87,7 @@
     <t>Fee</t>
   </si>
   <si>
-    <t>#des</t>
+    <t>desc</t>
   </si>
   <si>
     <t>Id</t>
@@ -97,6 +97,24 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>提高攻击倍率</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>提高防御倍率</t>
+  </si>
+  <si>
+    <t>血量</t>
+  </si>
+  <si>
+    <t>提高生命倍率</t>
   </si>
   <si>
     <t>铜墙</t>
@@ -768,9 +786,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1098,225 +1117,229 @@
   <dimension ref="A1:N34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2"/>
+    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="7" width="13.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.25" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="3" customWidth="1"/>
     <col min="11" max="11" width="34.625" style="1" customWidth="1"/>
     <col min="12" max="12" width="30.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.625" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="13" max="13" width="8.125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="9.625" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+      <c r="K4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="5"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C6" s="1">
+      <c r="K5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="5"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
         <v>10</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <v>14</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="2">
         <v>100</v>
       </c>
-      <c r="J6" s="1">
-        <v>300</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C7" s="1">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
         <v>10</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
         <v>16</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="2">
         <v>100</v>
       </c>
-      <c r="J7" s="1">
-        <v>300</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C8" s="1">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C8" s="2">
         <v>3</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
         <v>1</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="2">
         <v>26</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="2">
         <v>100</v>
       </c>
-      <c r="J8" s="1">
-        <v>300</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -1329,23 +1352,23 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H9" s="1">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I9" s="1">
         <v>100</v>
       </c>
       <c r="J9" s="1">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C10" s="1">
+      <c r="C10" s="2">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1361,21 +1384,105 @@
         <v>10</v>
       </c>
       <c r="H10" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" s="1">
         <v>100</v>
       </c>
       <c r="J10" s="1">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1"/>
-    <row r="12" s="1" customFormat="1" customHeight="1"/>
-    <row r="13" s="1" customFormat="1" customHeight="1"/>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C11" s="2">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>26</v>
+      </c>
+      <c r="I11" s="1">
+        <v>100</v>
+      </c>
+      <c r="J11" s="1">
+        <v>10</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C12" s="2">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>27</v>
+      </c>
+      <c r="I12" s="1">
+        <v>100</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C13" s="2">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1">
+        <v>15</v>
+      </c>
+      <c r="I13" s="1">
+        <v>100</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
     <row r="16" s="1" customFormat="1" customHeight="1"/>
@@ -1447,7 +1554,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:F3 G3 H3:J3 E4:F4 G4 H4:I4 J4 E5:F5 G5 H5:J5 C3:C5 D4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -99,52 +99,52 @@
     <t>string</t>
   </si>
   <si>
-    <t>攻击</t>
+    <t>绝杀</t>
   </si>
   <si>
     <t>提高攻击倍率</t>
   </si>
   <si>
-    <t>防御</t>
+    <t>固守</t>
   </si>
   <si>
     <t>提高防御倍率</t>
   </si>
   <si>
-    <t>血量</t>
+    <t>命源</t>
   </si>
   <si>
     <t>提高生命倍率</t>
   </si>
   <si>
-    <t>铜墙</t>
+    <t>铁壁</t>
   </si>
   <si>
     <t>提高防御系数</t>
   </si>
   <si>
-    <t>铁壁</t>
-  </si>
-  <si>
-    <t>所受伤害不会超过生命上限x%</t>
-  </si>
-  <si>
-    <t>神之减伤</t>
+    <t>破军</t>
+  </si>
+  <si>
+    <t>溢出的暴击率，每点会额外增加x%的伤害</t>
+  </si>
+  <si>
+    <t>贪狼</t>
+  </si>
+  <si>
+    <t>附加自身生命上限*x%的伤害，不计入吸血</t>
+  </si>
+  <si>
+    <t>律己</t>
+  </si>
+  <si>
+    <t>拥有护体盾的时候，任意伤害不会超过护盾的x%</t>
+  </si>
+  <si>
+    <t>镇卫</t>
   </si>
   <si>
     <t>溢出的减伤倍率，会额外计算</t>
-  </si>
-  <si>
-    <t>神之暴击</t>
-  </si>
-  <si>
-    <t>溢出的暴击率，每点会额外增加x%的伤害</t>
-  </si>
-  <si>
-    <t>血杀</t>
-  </si>
-  <si>
-    <t>附加自身生命上限*x%的伤害，不计入吸血</t>
   </si>
 </sst>
 </file>
@@ -321,12 +321,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1114,7 +1114,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H8" s="2">
         <v>26</v>
@@ -1381,10 +1381,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1">
         <v>100</v>
@@ -1410,16 +1410,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H11" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I11" s="1">
         <v>100</v>
       </c>
       <c r="J11" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>23</v>
@@ -1439,10 +1439,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H12" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I12" s="1">
         <v>100</v>
@@ -1468,16 +1468,16 @@
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I13" s="1">
         <v>100</v>
       </c>
       <c r="J13" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>27</v>
@@ -1486,8 +1486,14 @@
     <row r="14" s="1" customFormat="1" customHeight="1"/>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
     <row r="16" s="1" customFormat="1" customHeight="1"/>
-    <row r="17" s="1" customFormat="1" customHeight="1"/>
-    <row r="18" s="1" customFormat="1" customHeight="1"/>
+    <row r="17" customHeight="1" spans="9:10">
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="9:10">
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
     <row r="19" customHeight="1" spans="9:10">
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1543,14 +1549,6 @@
     <row r="32" customHeight="1" spans="9:10">
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="9:10">
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="9:10">
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="L3" authorId="0">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -84,6 +84,9 @@
     <t>AttrValue</t>
   </si>
   <si>
+    <t>RiseValue</t>
+  </si>
+  <si>
     <t>Fee</t>
   </si>
   <si>
@@ -102,25 +105,25 @@
     <t>绝杀</t>
   </si>
   <si>
-    <t>提高攻击倍率</t>
+    <t>提高攻击倍率{0}%</t>
   </si>
   <si>
     <t>固守</t>
   </si>
   <si>
-    <t>提高防御倍率</t>
+    <t>提高防御倍率{0}%</t>
   </si>
   <si>
     <t>命源</t>
   </si>
   <si>
-    <t>提高生命倍率</t>
+    <t>提高生命倍率{0}%</t>
   </si>
   <si>
     <t>铁壁</t>
   </si>
   <si>
-    <t>提高防御系数</t>
+    <t>提高防御系数{0}点</t>
   </si>
   <si>
     <t>破军</t>
@@ -321,12 +324,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1114,7 +1117,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1122,34 +1125,36 @@
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="7" width="13.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="16.375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="34.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="30.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="9.625" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3"/>
+    <col min="9" max="10" width="16.375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.5" style="3" customWidth="1"/>
+    <col min="12" max="12" width="34.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="30.125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.625" style="3" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
-      <c r="M1" s="3"/>
+      <c r="K1" s="3"/>
       <c r="N1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="K2" s="3"/>
       <c r="N2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="s">
@@ -1176,18 +1181,21 @@
       <c r="J3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="3"/>
+      <c r="L3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="5"/>
       <c r="N3" s="3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
@@ -1210,53 +1218,59 @@
       <c r="J4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="3"/>
+      <c r="L4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="5"/>
       <c r="N4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="3"/>
+      <c r="K5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="5"/>
       <c r="N5" s="3"/>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -1265,27 +1279,30 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2">
-        <v>14</v>
+        <v>2001</v>
       </c>
       <c r="I6" s="2">
         <v>100</v>
       </c>
       <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
         <v>1</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
@@ -1294,27 +1311,30 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2">
-        <v>16</v>
+        <v>2002</v>
       </c>
       <c r="I7" s="2">
         <v>100</v>
       </c>
       <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
         <v>1</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C8" s="2">
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
@@ -1323,56 +1343,62 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2">
-        <v>26</v>
+        <v>2003</v>
       </c>
       <c r="I8" s="2">
         <v>100</v>
       </c>
       <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
         <v>1</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
         <v>10</v>
       </c>
       <c r="H9" s="1">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="I9" s="1">
-        <v>100</v>
-      </c>
-      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
         <v>2</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C10" s="2">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -1384,24 +1410,27 @@
         <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="I10" s="1">
         <v>100</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
         <v>2</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="2">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -1413,24 +1442,27 @@
         <v>10</v>
       </c>
       <c r="H11" s="1">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="I11" s="1">
         <v>100</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>2</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C12" s="2">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -1442,24 +1474,27 @@
         <v>10</v>
       </c>
       <c r="H12" s="1">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="I12" s="1">
-        <v>100</v>
-      </c>
-      <c r="J12" s="1">
+        <v>9</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
         <v>2</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C13" s="2">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -1471,88 +1506,107 @@
         <v>1</v>
       </c>
       <c r="H13" s="1">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="I13" s="1">
         <v>100</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
         <v>10</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>27</v>
+      <c r="L13" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
     <row r="16" s="1" customFormat="1" customHeight="1"/>
-    <row r="17" customHeight="1" spans="9:10">
+    <row r="17" customHeight="1" spans="9:11">
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="9:10">
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="9:11">
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="9:10">
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="9:11">
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
-    </row>
-    <row r="20" customHeight="1" spans="9:10">
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" customHeight="1" spans="9:11">
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" spans="9:10">
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" customHeight="1" spans="9:11">
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-    </row>
-    <row r="22" customHeight="1" spans="9:10">
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" customHeight="1" spans="9:11">
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="9:10">
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" customHeight="1" spans="9:11">
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="9:10">
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" customHeight="1" spans="9:11">
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="9:10">
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" customHeight="1" spans="9:11">
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="9:10">
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" customHeight="1" spans="9:11">
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-    </row>
-    <row r="27" customHeight="1" spans="9:10">
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" customHeight="1" spans="9:11">
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="9:10">
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" customHeight="1" spans="9:11">
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-    </row>
-    <row r="29" customHeight="1" spans="9:10">
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" customHeight="1" spans="9:11">
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-    </row>
-    <row r="30" customHeight="1" spans="9:10">
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" customHeight="1" spans="9:11">
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="9:10">
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="9:11">
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="9:10">
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" customHeight="1" spans="9:11">
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3 J4 J5 K3:K5 C3:I5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1404,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
         <v>10</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1606,7 +1606,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3 J4 J5 K3:K5 C3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,30 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="M3" authorId="0">
+    <comment ref="J3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 加法
+2 乘法</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -84,9 +107,15 @@
     <t>AttrValue</t>
   </si>
   <si>
+    <t>RiseType</t>
+  </si>
+  <si>
     <t>RiseValue</t>
   </si>
   <si>
+    <t>RiseUnit</t>
+  </si>
+  <si>
     <t>Fee</t>
   </si>
   <si>
@@ -105,6 +134,9 @@
     <t>绝杀</t>
   </si>
   <si>
+    <t>%</t>
+  </si>
+  <si>
     <t>提高攻击倍率{0}%</t>
   </si>
   <si>
@@ -123,25 +155,31 @@
     <t>铁壁</t>
   </si>
   <si>
+    <t>点</t>
+  </si>
+  <si>
     <t>提高防御系数{0}点</t>
   </si>
   <si>
     <t>破军</t>
   </si>
   <si>
-    <t>溢出的暴击率，每点会额外增加x%的伤害</t>
+    <t>溢出的暴击率，每点会额外增加{0}%的伤害</t>
   </si>
   <si>
     <t>贪狼</t>
   </si>
   <si>
-    <t>附加自身生命上限*x%的伤害，不计入吸血</t>
+    <t>倍</t>
+  </si>
+  <si>
+    <t>附加自身生命上限*{0}的伤害，不计入吸血</t>
   </si>
   <si>
     <t>律己</t>
   </si>
   <si>
-    <t>拥有护体盾的时候，任意伤害不会超过护盾的x%</t>
+    <t>拥有护体盾的时候，任意伤害不会超过面板生命的（100-{0}）%</t>
   </si>
   <si>
     <t>镇卫</t>
@@ -1117,7 +1155,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1126,35 +1164,40 @@
     <col min="4" max="7" width="13.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.25" style="3" customWidth="1"/>
     <col min="9" max="10" width="16.375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="34.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="30.125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="9.625" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="3"/>
+    <col min="11" max="12" width="13.25" style="3" customWidth="1"/>
+    <col min="13" max="13" width="14.5" style="3" customWidth="1"/>
+    <col min="14" max="14" width="43.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="30.125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.125" style="3" customWidth="1"/>
+    <col min="17" max="17" width="9.625" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="s">
@@ -1184,18 +1227,24 @@
       <c r="K3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="M3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="5"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
@@ -1221,56 +1270,68 @@
       <c r="K4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="M4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="5"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>13</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="5"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -1288,21 +1349,27 @@
         <v>100</v>
       </c>
       <c r="J6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2">
+        <v>100</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="2">
         <v>1</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="N6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
@@ -1320,21 +1387,27 @@
         <v>100</v>
       </c>
       <c r="J7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M7" s="2">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="2">
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
@@ -1352,21 +1425,27 @@
         <v>100</v>
       </c>
       <c r="J8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2">
+        <v>100</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="2">
         <v>1</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="N8" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -1384,21 +1463,27 @@
         <v>1</v>
       </c>
       <c r="J9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="1">
         <v>2</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="N9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C10" s="2">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -1416,21 +1501,27 @@
         <v>100</v>
       </c>
       <c r="J10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="1">
         <v>2</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="N10" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C11" s="2">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -1448,21 +1539,27 @@
         <v>100</v>
       </c>
       <c r="J11" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1">
+        <v>10</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="1">
         <v>2</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="N11" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C12" s="2">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -1480,21 +1577,27 @@
         <v>9</v>
       </c>
       <c r="J12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
+        <v>9</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="1">
         <v>2</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="N12" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C13" s="2">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -1509,104 +1612,140 @@
         <v>115</v>
       </c>
       <c r="I13" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
         <v>0</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1"/>
+      <c r="M13" s="1">
         <v>10</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>28</v>
+      <c r="N13" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
     <row r="16" s="1" customFormat="1" customHeight="1"/>
-    <row r="17" customHeight="1" spans="9:11">
+    <row r="17" customHeight="1" spans="9:13">
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="9:11">
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="9:13">
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="9:11">
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="9:13">
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-    </row>
-    <row r="20" customHeight="1" spans="9:11">
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+    </row>
+    <row r="20" customHeight="1" spans="9:13">
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" spans="9:11">
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+    </row>
+    <row r="21" customHeight="1" spans="9:13">
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-    </row>
-    <row r="22" customHeight="1" spans="9:11">
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+    </row>
+    <row r="22" customHeight="1" spans="9:13">
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="9:11">
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+    </row>
+    <row r="23" customHeight="1" spans="9:13">
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="9:11">
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+    </row>
+    <row r="24" customHeight="1" spans="9:13">
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="9:11">
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+    </row>
+    <row r="25" customHeight="1" spans="9:13">
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="9:11">
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+    </row>
+    <row r="26" customHeight="1" spans="9:13">
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-    </row>
-    <row r="27" customHeight="1" spans="9:11">
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+    </row>
+    <row r="27" customHeight="1" spans="9:13">
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="9:11">
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+    </row>
+    <row r="28" customHeight="1" spans="9:13">
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-    </row>
-    <row r="29" customHeight="1" spans="9:11">
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+    </row>
+    <row r="29" customHeight="1" spans="9:13">
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-    </row>
-    <row r="30" customHeight="1" spans="9:11">
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+    </row>
+    <row r="30" customHeight="1" spans="9:13">
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="9:11">
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="9:13">
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="9:11">
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+    </row>
+    <row r="32" customHeight="1" spans="9:13">
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3 L3 J4 L4 J5 L5 K3:K5 M3:M5 C3:I5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -155,10 +155,10 @@
     <t>铁壁</t>
   </si>
   <si>
-    <t>点</t>
-  </si>
-  <si>
-    <t>提高防御系数{0}点</t>
+    <t>倍</t>
+  </si>
+  <si>
+    <t>提高防御系数{0}倍</t>
   </si>
   <si>
     <t>破军</t>
@@ -170,10 +170,7 @@
     <t>贪狼</t>
   </si>
   <si>
-    <t>倍</t>
-  </si>
-  <si>
-    <t>附加自身生命上限*{0}的伤害，不计入吸血</t>
+    <t>附加自身生命上限*{0}倍的伤害，不计入吸血</t>
   </si>
   <si>
     <t>律己</t>
@@ -1460,13 +1457,13 @@
         <v>112</v>
       </c>
       <c r="I9" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>23</v>
@@ -1536,7 +1533,7 @@
         <v>114</v>
       </c>
       <c r="I11" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J11" s="2">
         <v>2</v>
@@ -1545,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M11" s="1">
         <v>2</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -1559,7 +1556,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -1589,7 +1586,7 @@
         <v>2</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -1597,7 +1594,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -1625,7 +1622,7 @@
         <v>10</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
@@ -1745,7 +1742,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3 L3 J4 L4 J5 L5 K3:K5 M3:M5 C3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -131,55 +131,67 @@
     <t>string</t>
   </si>
   <si>
+    <t>破军</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>提高攻击倍率{0}%</t>
+  </si>
+  <si>
+    <t>镇卫</t>
+  </si>
+  <si>
+    <t>提高防御倍率{0}%</t>
+  </si>
+  <si>
+    <t>命源</t>
+  </si>
+  <si>
+    <t>提高生命倍率{0}%</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>提高闪避概率{0}%</t>
+  </si>
+  <si>
+    <t>铁壁</t>
+  </si>
+  <si>
+    <t>倍</t>
+  </si>
+  <si>
+    <t>提高防御系数{0}倍</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>提高命中概率{0}%</t>
+  </si>
+  <si>
     <t>绝杀</t>
   </si>
   <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>提高攻击倍率{0}%</t>
+    <t>溢出的暴击率，每点会额外增加{0}%的伤害</t>
+  </si>
+  <si>
+    <t>贪狼</t>
+  </si>
+  <si>
+    <t>附加自身生命上限*{0}倍的伤害，不计入吸血</t>
+  </si>
+  <si>
+    <t>律己</t>
+  </si>
+  <si>
+    <t>拥有护体盾的时候，任意伤害不会超过面板生命的（100-{0}）%</t>
   </si>
   <si>
     <t>固守</t>
-  </si>
-  <si>
-    <t>提高防御倍率{0}%</t>
-  </si>
-  <si>
-    <t>命源</t>
-  </si>
-  <si>
-    <t>提高生命倍率{0}%</t>
-  </si>
-  <si>
-    <t>铁壁</t>
-  </si>
-  <si>
-    <t>倍</t>
-  </si>
-  <si>
-    <t>提高防御系数{0}倍</t>
-  </si>
-  <si>
-    <t>破军</t>
-  </si>
-  <si>
-    <t>溢出的暴击率，每点会额外增加{0}%的伤害</t>
-  </si>
-  <si>
-    <t>贪狼</t>
-  </si>
-  <si>
-    <t>附加自身生命上限*{0}倍的伤害，不计入吸血</t>
-  </si>
-  <si>
-    <t>律己</t>
-  </si>
-  <si>
-    <t>拥有护体盾的时候，任意伤害不会超过面板生命的（100-{0}）%</t>
-  </si>
-  <si>
-    <t>镇卫</t>
   </si>
   <si>
     <t>溢出的减伤倍率，会额外计算</t>
@@ -1152,7 +1164,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -1337,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H6" s="2">
         <v>2001</v>
@@ -1375,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H7" s="2">
         <v>2002</v>
@@ -1413,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H8" s="2">
         <v>2003</v>
@@ -1437,11 +1449,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="1">
@@ -1457,30 +1469,30 @@
         <v>112</v>
       </c>
       <c r="I9" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="M9" s="1">
         <v>2</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="N9" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C10" s="2">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -1489,22 +1501,22 @@
         <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H10" s="1">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I10" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="J10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="M10" s="1">
         <v>2</v>
@@ -1517,7 +1529,7 @@
       <c r="C11" s="2">
         <v>6</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="1">
@@ -1530,24 +1542,24 @@
         <v>10</v>
       </c>
       <c r="H11" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I11" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
         <v>2</v>
       </c>
-      <c r="K11" s="1">
-        <v>10</v>
-      </c>
       <c r="L11" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="M11" s="1">
         <v>2</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="N11" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1562,28 +1574,28 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G12" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H12" s="1">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I12" s="1">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="J12" s="2">
         <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="M12" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>30</v>
@@ -1600,48 +1612,109 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G13" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H13" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I13" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M13" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1"/>
-    <row r="15" s="1" customFormat="1" customHeight="1"/>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C14" s="2">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>20</v>
+      </c>
+      <c r="G14" s="1">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1">
+        <v>113</v>
+      </c>
+      <c r="I14" s="1">
+        <v>9</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>9</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="1">
+        <v>3</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>40</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>115</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>10</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
     <row r="16" s="1" customFormat="1" customHeight="1"/>
-    <row r="17" customHeight="1" spans="9:13">
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="9:13">
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1"/>
+    <row r="18" s="1" customFormat="1" customHeight="1"/>
     <row r="19" customHeight="1" spans="9:13">
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1739,6 +1812,20 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
+    </row>
+    <row r="33" customHeight="1" spans="9:13">
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="9:13">
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -152,7 +152,7 @@
     <t>提高生命倍率{0}%</t>
   </si>
   <si>
-    <t>闪避</t>
+    <t>迷踪</t>
   </si>
   <si>
     <t>提高闪避概率{0}%</t>
@@ -167,7 +167,7 @@
     <t>提高防御系数{0}倍</t>
   </si>
   <si>
-    <t>命中</t>
+    <t>天目</t>
   </si>
   <si>
     <t>提高命中概率{0}%</t>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1393,13 +1393,13 @@
         <v>2002</v>
       </c>
       <c r="I7" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J7" s="2">
         <v>1</v>
       </c>
       <c r="K7" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>16</v>
@@ -1431,13 +1431,13 @@
         <v>2003</v>
       </c>
       <c r="I8" s="2">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J8" s="2">
         <v>1</v>
       </c>
       <c r="K8" s="2">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>16</v>
@@ -1507,7 +1507,7 @@
         <v>112</v>
       </c>
       <c r="I10" s="1">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="J10" s="2">
         <v>2</v>
@@ -1621,7 +1621,7 @@
         <v>114</v>
       </c>
       <c r="I13" s="1">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="J13" s="2">
         <v>2</v>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1469,13 +1469,13 @@
         <v>112</v>
       </c>
       <c r="I9" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" s="2">
         <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>16</v>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1621,7 +1621,7 @@
         <v>114</v>
       </c>
       <c r="I13" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J13" s="2">
         <v>2</v>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -170,7 +170,7 @@
     <t>天目</t>
   </si>
   <si>
-    <t>提高命中概率{0}%</t>
+    <t>提高精准概率{0}%</t>
   </si>
   <si>
     <t>绝杀</t>
@@ -1466,7 +1466,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="1">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="I9" s="1">
         <v>3</v>
@@ -1542,7 +1542,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="1">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="I11" s="1">
         <v>2</v>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1577,19 +1577,19 @@
         <v>20</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H12" s="1">
         <v>116</v>
       </c>
       <c r="I12" s="1">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>16</v>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1592,7 +1592,7 @@
         <v>2</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="M12" s="1">
         <v>3</v>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="0">
+    <comment ref="P3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -84,11 +84,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -170,7 +173,7 @@
     <t>天目</t>
   </si>
   <si>
-    <t>提高精准概率{0}%</t>
+    <t>提高命中概率{0}%</t>
   </si>
   <si>
     <t>绝杀</t>
@@ -195,6 +198,87 @@
   </si>
   <si>
     <t>溢出的减伤倍率，会额外计算</t>
+  </si>
+  <si>
+    <t>生命·壹</t>
+  </si>
+  <si>
+    <t>防御·壹</t>
+  </si>
+  <si>
+    <t>韧性·壹</t>
+  </si>
+  <si>
+    <t>提高韧性倍率{0}%</t>
+  </si>
+  <si>
+    <t>物攻·壹</t>
+  </si>
+  <si>
+    <t>提高物攻倍率{0}%</t>
+  </si>
+  <si>
+    <t>魔攻·壹</t>
+  </si>
+  <si>
+    <t>提高魔法倍率{0}%</t>
+  </si>
+  <si>
+    <t>道攻·壹</t>
+  </si>
+  <si>
+    <t>提高道术倍率{0}%</t>
+  </si>
+  <si>
+    <t>命中·壹</t>
+  </si>
+  <si>
+    <t>提高命中{0}%</t>
+  </si>
+  <si>
+    <t>攻击·壹</t>
+  </si>
+  <si>
+    <t>闪避·壹</t>
+  </si>
+  <si>
+    <t>提高闪避{0}%</t>
+  </si>
+  <si>
+    <t>神话·壹</t>
+  </si>
+  <si>
+    <t>提高神话基础属性{0}%</t>
+  </si>
+  <si>
+    <t>生命·贰</t>
+  </si>
+  <si>
+    <t>防御·贰</t>
+  </si>
+  <si>
+    <t>韧性·贰</t>
+  </si>
+  <si>
+    <t>物攻·贰</t>
+  </si>
+  <si>
+    <t>魔攻·贰</t>
+  </si>
+  <si>
+    <t>道攻·贰</t>
+  </si>
+  <si>
+    <t>命中·贰</t>
+  </si>
+  <si>
+    <t>攻击·贰</t>
+  </si>
+  <si>
+    <t>闪避·贰</t>
+  </si>
+  <si>
+    <t>神话·贰</t>
   </si>
 </sst>
 </file>
@@ -371,12 +455,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1164,49 +1248,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="9" style="3"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="7" width="13.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.25" style="3" customWidth="1"/>
-    <col min="9" max="10" width="16.375" style="3" customWidth="1"/>
-    <col min="11" max="12" width="13.25" style="3" customWidth="1"/>
-    <col min="13" max="13" width="14.5" style="3" customWidth="1"/>
-    <col min="14" max="14" width="43.25" style="1" customWidth="1"/>
-    <col min="15" max="15" width="30.125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.125" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.625" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="3"/>
+    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
+    <col min="5" max="8" width="13.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.25" style="3" customWidth="1"/>
+    <col min="10" max="11" width="16.375" style="3" customWidth="1"/>
+    <col min="12" max="13" width="13.25" style="3" customWidth="1"/>
+    <col min="14" max="14" width="14.5" style="3" customWidth="1"/>
+    <col min="15" max="15" width="43.25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="30.125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8.125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.625" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
-      <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
-      <c r="P1" s="3"/>
+      <c r="N1" s="3"/>
       <c r="Q1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="R1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="P2" s="3"/>
+      <c r="N2" s="3"/>
       <c r="Q2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="R2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="s">
@@ -1242,18 +1326,21 @@
       <c r="M3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="5"/>
-      <c r="P3" s="3"/>
+      <c r="O3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="5"/>
       <c r="Q3" s="3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="R3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
@@ -1285,551 +1372,1295 @@
       <c r="M4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="5"/>
-      <c r="P4" s="3"/>
+      <c r="O4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="5"/>
       <c r="Q4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="R4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="5"/>
-      <c r="P5" s="3"/>
+      <c r="O5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="P5" s="5"/>
       <c r="Q5" s="3"/>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
+        <v>10</v>
+      </c>
+      <c r="I6" s="2">
         <v>2001</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2">
         <v>100</v>
       </c>
-      <c r="J6" s="2">
-        <v>1</v>
-      </c>
       <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2">
         <v>100</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" s="2">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="N6" s="2">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2">
+        <v>10</v>
+      </c>
+      <c r="I7" s="2">
         <v>2002</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>200</v>
       </c>
-      <c r="J7" s="2">
-        <v>1</v>
-      </c>
       <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
         <v>200</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M7" s="2">
-        <v>1</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="M7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C8" s="2">
         <v>3</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2">
+        <v>10</v>
+      </c>
+      <c r="I8" s="2">
         <v>2003</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2">
         <v>300</v>
       </c>
-      <c r="J8" s="2">
-        <v>1</v>
-      </c>
       <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2">
         <v>300</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M8" s="2">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="M8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="F9" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>10</v>
       </c>
       <c r="H9" s="1">
+        <v>10</v>
+      </c>
+      <c r="I9" s="1">
         <v>31</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>3</v>
       </c>
-      <c r="J9" s="2">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
         <v>3</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M9" s="1">
-        <v>2</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="M9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="1">
+        <v>2</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C10" s="2">
         <v>5</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="F10" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>10</v>
       </c>
       <c r="H10" s="1">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1">
         <v>112</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>100</v>
       </c>
-      <c r="J10" s="2">
-        <v>2</v>
-      </c>
-      <c r="K10" s="1">
+      <c r="K10" s="2">
+        <v>2</v>
+      </c>
+      <c r="L10" s="1">
         <v>6</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="1">
-        <v>2</v>
-      </c>
-      <c r="N10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="N10" s="1">
+        <v>2</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C11" s="2">
         <v>6</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F11" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>10</v>
       </c>
       <c r="H11" s="1">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1">
         <v>32</v>
       </c>
-      <c r="I11" s="1">
-        <v>2</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>2</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M11" s="1">
-        <v>2</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="J11" s="1">
+        <v>2</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>2</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="1">
+        <v>2</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C12" s="2">
         <v>7</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
         <v>20</v>
       </c>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
       <c r="H12" s="1">
+        <v>10</v>
+      </c>
+      <c r="I12" s="1">
         <v>116</v>
       </c>
-      <c r="I12" s="1">
-        <v>2</v>
-      </c>
-      <c r="J12" s="2">
-        <v>2</v>
-      </c>
-      <c r="K12" s="1">
-        <v>2</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="1">
+      <c r="J12" s="1">
+        <v>2</v>
+      </c>
+      <c r="K12" s="2">
+        <v>2</v>
+      </c>
+      <c r="L12" s="1">
+        <v>2</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" s="1">
         <v>3</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O12" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C13" s="2">
         <v>8</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0</v>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
         <v>20</v>
       </c>
-      <c r="G13" s="1">
-        <v>10</v>
-      </c>
       <c r="H13" s="1">
+        <v>10</v>
+      </c>
+      <c r="I13" s="1">
         <v>114</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>100</v>
       </c>
-      <c r="J13" s="2">
-        <v>2</v>
-      </c>
-      <c r="K13" s="1">
-        <v>10</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="1">
+      <c r="K13" s="2">
+        <v>2</v>
+      </c>
+      <c r="L13" s="1">
+        <v>10</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="1">
         <v>3</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O13" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C14" s="2">
         <v>9</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0</v>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
         <v>20</v>
       </c>
-      <c r="G14" s="1">
-        <v>10</v>
-      </c>
       <c r="H14" s="1">
+        <v>10</v>
+      </c>
+      <c r="I14" s="1">
         <v>113</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>9</v>
       </c>
-      <c r="J14" s="2">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1">
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
         <v>9</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="1">
+      <c r="M14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" s="1">
         <v>3</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O14" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C15" s="2">
         <v>10</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0</v>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
         <v>40</v>
       </c>
-      <c r="G15" s="1">
-        <v>1</v>
-      </c>
       <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
         <v>115</v>
       </c>
-      <c r="I15" s="1">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2">
-        <v>1</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>10</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>36</v>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>10</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1"/>
     <row r="17" s="1" customFormat="1" customHeight="1"/>
     <row r="18" s="1" customFormat="1" customHeight="1"/>
-    <row r="19" customHeight="1" spans="9:13">
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-    </row>
-    <row r="20" customHeight="1" spans="9:13">
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" spans="9:13">
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-    </row>
-    <row r="22" customHeight="1" spans="9:13">
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="9:13">
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="9:13">
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="9:13">
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="9:13">
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-    </row>
-    <row r="27" customHeight="1" spans="9:13">
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="9:13">
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-    </row>
-    <row r="29" customHeight="1" spans="9:13">
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-    </row>
-    <row r="30" customHeight="1" spans="9:13">
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="9:13">
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="9:13">
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="9:13">
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="9:13">
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C19" s="2">
+        <v>101</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>10</v>
+      </c>
+      <c r="I19" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J19" s="2">
+        <v>30</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2">
+        <v>30</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" s="2">
+        <v>1</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C20" s="2">
+        <v>102</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>10</v>
+      </c>
+      <c r="I20" s="2">
+        <v>2002</v>
+      </c>
+      <c r="J20" s="2">
+        <v>25</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2">
+        <v>25</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" s="2">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C21" s="2">
+        <v>103</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>10</v>
+      </c>
+      <c r="I21" s="2">
+        <v>2003</v>
+      </c>
+      <c r="J21" s="2">
+        <v>20</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2">
+        <v>20</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" s="2">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C22" s="2">
+        <v>104</v>
+      </c>
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>10</v>
+      </c>
+      <c r="I22" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J22" s="2">
+        <v>10</v>
+      </c>
+      <c r="K22" s="2">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2">
+        <v>10</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" s="2">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C23" s="2">
+        <v>105</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>10</v>
+      </c>
+      <c r="I23" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J23" s="2">
+        <v>10</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2">
+        <v>10</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="2">
+        <v>1</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C24" s="2">
+        <v>106</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>10</v>
+      </c>
+      <c r="I24" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J24" s="2">
+        <v>10</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2">
+        <v>10</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" s="2">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C25" s="2">
+        <v>107</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>10</v>
+      </c>
+      <c r="I25" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2">
+        <v>1</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" s="2">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C26" s="2">
+        <v>108</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>10</v>
+      </c>
+      <c r="I26" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J26" s="2">
+        <v>10</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2">
+        <v>10</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" s="2">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C27" s="2">
+        <v>109</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>10</v>
+      </c>
+      <c r="I27" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2">
+        <v>1</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" s="2">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C28" s="2">
+        <v>110</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>10</v>
+      </c>
+      <c r="I28" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2">
+        <v>1</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" s="2">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C29" s="2">
+        <v>111</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>10</v>
+      </c>
+      <c r="I29" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J29" s="2">
+        <v>30</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2">
+        <v>30</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" s="2">
+        <v>1</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C30" s="2">
+        <v>112</v>
+      </c>
+      <c r="D30" s="2">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>10</v>
+      </c>
+      <c r="I30" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J30" s="2">
+        <v>25</v>
+      </c>
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2">
+        <v>25</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" s="2">
+        <v>1</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C31" s="2">
+        <v>113</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>10</v>
+      </c>
+      <c r="I31" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J31" s="2">
+        <v>20</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2">
+        <v>20</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" s="2">
+        <v>1</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C32" s="2">
+        <v>114</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>10</v>
+      </c>
+      <c r="I32" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J32" s="2">
+        <v>10</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2">
+        <v>10</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" s="2">
+        <v>1</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C33" s="2">
+        <v>115</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2">
+        <v>10</v>
+      </c>
+      <c r="I33" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J33" s="2">
+        <v>10</v>
+      </c>
+      <c r="K33" s="2">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2">
+        <v>10</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N33" s="2">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C34" s="2">
+        <v>116</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2">
+        <v>10</v>
+      </c>
+      <c r="I34" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J34" s="2">
+        <v>10</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2">
+        <v>10</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" s="2">
+        <v>1</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C35" s="2">
+        <v>117</v>
+      </c>
+      <c r="D35" s="2">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2">
+        <v>10</v>
+      </c>
+      <c r="I35" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J35" s="2">
+        <v>1</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2">
+        <v>1</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" s="2">
+        <v>1</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C36" s="2">
+        <v>118</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>10</v>
+      </c>
+      <c r="I36" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J36" s="2">
+        <v>10</v>
+      </c>
+      <c r="K36" s="2">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2">
+        <v>10</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" s="2">
+        <v>1</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C37" s="2">
+        <v>119</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>10</v>
+      </c>
+      <c r="I37" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J37" s="2">
+        <v>1</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2">
+        <v>1</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" s="2">
+        <v>1</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:15">
+      <c r="C38" s="2">
+        <v>120</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2">
+        <v>10</v>
+      </c>
+      <c r="I38" s="2">
+        <v>2001</v>
+      </c>
+      <c r="J38" s="2">
+        <v>1</v>
+      </c>
+      <c r="K38" s="2">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2">
+        <v>1</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" s="2">
+        <v>1</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="K3" authorId="0">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -95,6 +95,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Logo</t>
+  </si>
+  <si>
     <t>RequireId</t>
   </si>
   <si>
@@ -245,10 +248,22 @@
     <t>提高闪避{0}%</t>
   </si>
   <si>
-    <t>神话·壹</t>
-  </si>
-  <si>
-    <t>提高神话基础属性{0}%</t>
+    <t>神命·壹</t>
+  </si>
+  <si>
+    <t>提高神话基础生命{0}%</t>
+  </si>
+  <si>
+    <t>神攻·壹</t>
+  </si>
+  <si>
+    <t>提高神话基础攻击{0}%</t>
+  </si>
+  <si>
+    <t>神御·壹</t>
+  </si>
+  <si>
+    <t>提高神话基础防御{0}%</t>
   </si>
   <si>
     <t>生命·贰</t>
@@ -278,7 +293,13 @@
     <t>闪避·贰</t>
   </si>
   <si>
-    <t>神话·贰</t>
+    <t>神命·贰</t>
+  </si>
+  <si>
+    <t>神攻·贰</t>
+  </si>
+  <si>
+    <t>神御·贰</t>
   </si>
 </sst>
 </file>
@@ -455,23 +476,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -796,7 +823,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -820,16 +847,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -838,97 +865,98 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1248,187 +1276,196 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3"/>
+    <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9" style="4"/>
     <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
-    <col min="5" max="8" width="13.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.25" style="3" customWidth="1"/>
-    <col min="10" max="11" width="16.375" style="3" customWidth="1"/>
-    <col min="12" max="13" width="13.25" style="3" customWidth="1"/>
-    <col min="14" max="14" width="14.5" style="3" customWidth="1"/>
-    <col min="15" max="15" width="43.25" style="1" customWidth="1"/>
-    <col min="16" max="16" width="30.125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.125" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9.625" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="3"/>
+    <col min="5" max="9" width="13.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.25" style="4" customWidth="1"/>
+    <col min="11" max="12" width="16.375" style="4" customWidth="1"/>
+    <col min="13" max="14" width="13.25" style="4" customWidth="1"/>
+    <col min="15" max="15" width="14.5" style="4" customWidth="1"/>
+    <col min="16" max="16" width="43.25" style="1" customWidth="1"/>
+    <col min="17" max="17" width="30.125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.125" style="4" customWidth="1"/>
+    <col min="19" max="19" width="9.625" style="4" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" s="4" t="s">
+      <c r="M3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4" t="s">
+      <c r="P3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="Q3" s="6"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="4" t="s">
+      <c r="M4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="P4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>14</v>
+      <c r="E5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1436,40 +1473,43 @@
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
+        <v>10</v>
+      </c>
+      <c r="J6" s="2">
         <v>2001</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <v>100</v>
       </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
       <c r="L6" s="2">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2">
         <v>100</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N6" s="2">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O6" s="2">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1477,40 +1517,43 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
+        <v>10</v>
+      </c>
+      <c r="J7" s="2">
         <v>2002</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>200</v>
       </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
       <c r="L7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2">
         <v>200</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" s="2">
-        <v>1</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" s="2">
+        <v>1</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1518,40 +1561,43 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
+        <v>10</v>
+      </c>
+      <c r="J8" s="2">
         <v>2003</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <v>300</v>
       </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
       <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2">
         <v>300</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N8" s="2">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" s="2">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1559,40 +1605,43 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G9" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
         <v>10</v>
       </c>
       <c r="I9" s="1">
+        <v>10</v>
+      </c>
+      <c r="J9" s="1">
         <v>31</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>3</v>
       </c>
-      <c r="K9" s="2">
-        <v>1</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
         <v>3</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N9" s="1">
-        <v>2</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" s="1">
+        <v>2</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1600,40 +1649,43 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G10" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
         <v>10</v>
       </c>
       <c r="I10" s="1">
+        <v>10</v>
+      </c>
+      <c r="J10" s="1">
         <v>112</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>100</v>
       </c>
-      <c r="K10" s="2">
-        <v>2</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="L10" s="2">
+        <v>2</v>
+      </c>
+      <c r="M10" s="1">
         <v>6</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" s="1">
-        <v>2</v>
-      </c>
-      <c r="O10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O10" s="1">
+        <v>2</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="2">
         <v>6</v>
       </c>
@@ -1641,40 +1693,43 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="G11" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
       </c>
       <c r="I11" s="1">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1">
         <v>32</v>
       </c>
-      <c r="J11" s="1">
-        <v>2</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1">
-        <v>2</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N11" s="1">
-        <v>2</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="K11" s="1">
+        <v>2</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
+        <v>2</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" s="1">
+        <v>2</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -1682,40 +1737,43 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>20</v>
       </c>
-      <c r="H12" s="1">
-        <v>10</v>
-      </c>
       <c r="I12" s="1">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1">
         <v>116</v>
       </c>
-      <c r="J12" s="1">
-        <v>2</v>
-      </c>
-      <c r="K12" s="2">
-        <v>2</v>
-      </c>
-      <c r="L12" s="1">
-        <v>2</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N12" s="1">
+      <c r="K12" s="1">
+        <v>2</v>
+      </c>
+      <c r="L12" s="2">
+        <v>2</v>
+      </c>
+      <c r="M12" s="1">
+        <v>2</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="1">
         <v>3</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P12" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -1723,40 +1781,43 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
         <v>20</v>
       </c>
-      <c r="H13" s="1">
-        <v>10</v>
-      </c>
       <c r="I13" s="1">
+        <v>10</v>
+      </c>
+      <c r="J13" s="1">
         <v>114</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>100</v>
       </c>
-      <c r="K13" s="2">
-        <v>2</v>
-      </c>
-      <c r="L13" s="1">
-        <v>10</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" s="1">
+      <c r="L13" s="2">
+        <v>2</v>
+      </c>
+      <c r="M13" s="1">
+        <v>10</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="1">
         <v>3</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P13" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -1764,40 +1825,43 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <v>20</v>
       </c>
-      <c r="H14" s="1">
-        <v>10</v>
-      </c>
       <c r="I14" s="1">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1">
         <v>113</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>9</v>
       </c>
-      <c r="K14" s="2">
-        <v>1</v>
-      </c>
-      <c r="L14" s="1">
+      <c r="L14" s="2">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
         <v>9</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N14" s="1">
+      <c r="N14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" s="1">
         <v>3</v>
       </c>
-      <c r="O14" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P14" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -1805,40 +1869,43 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
         <v>40</v>
       </c>
-      <c r="H15" s="1">
-        <v>1</v>
-      </c>
       <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
         <v>115</v>
       </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="K15" s="2">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
-        <v>10</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>37</v>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>10</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1"/>
     <row r="17" s="1" customFormat="1" customHeight="1"/>
     <row r="18" s="1" customFormat="1" customHeight="1"/>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C19" s="2">
         <v>101</v>
       </c>
@@ -1846,40 +1913,43 @@
         <v>2</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="2">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="I19" s="2">
+        <v>10</v>
+      </c>
+      <c r="J19" s="2">
         <v>2001</v>
       </c>
-      <c r="J19" s="2">
+      <c r="K19" s="2">
         <v>30</v>
       </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
       <c r="L19" s="2">
+        <v>1</v>
+      </c>
+      <c r="M19" s="2">
         <v>30</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N19" s="2">
-        <v>1</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" s="2">
+        <v>1</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C20" s="2">
         <v>102</v>
       </c>
@@ -1887,40 +1957,43 @@
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20" s="2">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="I20" s="2">
+        <v>10</v>
+      </c>
+      <c r="J20" s="2">
         <v>2002</v>
       </c>
-      <c r="J20" s="2">
+      <c r="K20" s="2">
         <v>25</v>
       </c>
-      <c r="K20" s="2">
-        <v>1</v>
-      </c>
       <c r="L20" s="2">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2">
         <v>25</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N20" s="2">
-        <v>1</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" s="2">
+        <v>1</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C21" s="2">
         <v>103</v>
       </c>
@@ -1928,40 +2001,43 @@
         <v>2</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
       </c>
       <c r="H21" s="2">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="I21" s="2">
+        <v>10</v>
+      </c>
+      <c r="J21" s="2">
         <v>2003</v>
       </c>
-      <c r="J21" s="2">
+      <c r="K21" s="2">
         <v>20</v>
       </c>
-      <c r="K21" s="2">
-        <v>1</v>
-      </c>
       <c r="L21" s="2">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2">
         <v>20</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N21" s="2">
-        <v>1</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" s="2">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C22" s="2">
         <v>104</v>
       </c>
@@ -1969,40 +2045,44 @@
         <v>2</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="2">
-        <v>10</v>
+        <f t="shared" ref="H22:H36" si="0">H19+20</f>
+        <v>110</v>
       </c>
       <c r="I22" s="2">
+        <v>10</v>
+      </c>
+      <c r="J22" s="2">
         <v>2001</v>
       </c>
-      <c r="J22" s="2">
-        <v>10</v>
-      </c>
       <c r="K22" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L22" s="2">
-        <v>10</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N22" s="2">
-        <v>1</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2">
+        <v>10</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" s="2">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C23" s="2">
         <v>105</v>
       </c>
@@ -2010,40 +2090,44 @@
         <v>2</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>110</v>
       </c>
       <c r="I23" s="2">
+        <v>10</v>
+      </c>
+      <c r="J23" s="2">
         <v>2001</v>
       </c>
-      <c r="J23" s="2">
-        <v>10</v>
-      </c>
       <c r="K23" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L23" s="2">
-        <v>10</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N23" s="2">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2">
+        <v>10</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O23" s="2">
+        <v>1</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C24" s="2">
         <v>106</v>
       </c>
@@ -2051,40 +2135,44 @@
         <v>2</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>110</v>
       </c>
       <c r="I24" s="2">
+        <v>10</v>
+      </c>
+      <c r="J24" s="2">
         <v>2001</v>
       </c>
-      <c r="J24" s="2">
-        <v>10</v>
-      </c>
       <c r="K24" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L24" s="2">
-        <v>10</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N24" s="2">
-        <v>1</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2">
+        <v>10</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24" s="2">
+        <v>1</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C25" s="2">
         <v>107</v>
       </c>
@@ -2092,40 +2180,44 @@
         <v>2</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>130</v>
       </c>
       <c r="I25" s="2">
+        <v>10</v>
+      </c>
+      <c r="J25" s="2">
         <v>2001</v>
       </c>
-      <c r="J25" s="2">
-        <v>1</v>
-      </c>
       <c r="K25" s="2">
         <v>1</v>
       </c>
       <c r="L25" s="2">
         <v>1</v>
       </c>
-      <c r="M25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N25" s="2">
-        <v>1</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="M25" s="2">
+        <v>1</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" s="2">
+        <v>2</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C26" s="2">
         <v>108</v>
       </c>
@@ -2133,40 +2225,44 @@
         <v>2</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>130</v>
       </c>
       <c r="I26" s="2">
+        <v>10</v>
+      </c>
+      <c r="J26" s="2">
         <v>2001</v>
       </c>
-      <c r="J26" s="2">
-        <v>10</v>
-      </c>
       <c r="K26" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L26" s="2">
-        <v>10</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N26" s="2">
-        <v>1</v>
-      </c>
-      <c r="O26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M26" s="2">
+        <v>10</v>
+      </c>
+      <c r="N26" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O26" s="2">
+        <v>2</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C27" s="2">
         <v>109</v>
       </c>
@@ -2174,40 +2270,44 @@
         <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G27" s="2">
         <v>0</v>
       </c>
       <c r="H27" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>130</v>
       </c>
       <c r="I27" s="2">
+        <v>10</v>
+      </c>
+      <c r="J27" s="2">
         <v>2001</v>
       </c>
-      <c r="J27" s="2">
-        <v>1</v>
-      </c>
       <c r="K27" s="2">
         <v>1</v>
       </c>
       <c r="L27" s="2">
         <v>1</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N27" s="2">
-        <v>1</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="M27" s="2">
+        <v>1</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" s="2">
+        <v>2</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C28" s="2">
         <v>110</v>
       </c>
@@ -2215,22 +2315,23 @@
         <v>2</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
       </c>
       <c r="H28" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>150</v>
       </c>
       <c r="I28" s="2">
-        <v>2001</v>
+        <v>10</v>
       </c>
       <c r="J28" s="2">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="K28" s="2">
         <v>1</v>
@@ -2238,17 +2339,20 @@
       <c r="L28" s="2">
         <v>1</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N28" s="2">
-        <v>1</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="M28" s="2">
+        <v>1</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" s="2">
+        <v>3</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C29" s="2">
         <v>111</v>
       </c>
@@ -2256,40 +2360,44 @@
         <v>2</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>150</v>
       </c>
       <c r="I29" s="2">
-        <v>2001</v>
+        <v>10</v>
       </c>
       <c r="J29" s="2">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="K29" s="2">
         <v>1</v>
       </c>
       <c r="L29" s="2">
-        <v>30</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N29" s="2">
-        <v>1</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>1</v>
+      </c>
+      <c r="M29" s="2">
+        <v>1</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O29" s="2">
+        <v>3</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C30" s="2">
         <v>112</v>
       </c>
@@ -2297,81 +2405,89 @@
         <v>2</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
       </c>
       <c r="H30" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>150</v>
       </c>
       <c r="I30" s="2">
-        <v>2001</v>
+        <v>10</v>
       </c>
       <c r="J30" s="2">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="K30" s="2">
         <v>1</v>
       </c>
       <c r="L30" s="2">
-        <v>25</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N30" s="2">
-        <v>1</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>1</v>
+      </c>
+      <c r="M30" s="2">
+        <v>1</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O30" s="2">
+        <v>3</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" s="3" customFormat="1" customHeight="1" spans="3:16">
       <c r="C31" s="2">
         <v>113</v>
       </c>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2">
+      <c r="D31" s="3">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="3">
         <v>0</v>
       </c>
       <c r="H31" s="2">
-        <v>10</v>
-      </c>
-      <c r="I31" s="2">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="I31" s="3">
+        <v>10</v>
+      </c>
+      <c r="J31" s="3">
         <v>2001</v>
       </c>
-      <c r="J31" s="2">
-        <v>20</v>
-      </c>
-      <c r="K31" s="2">
-        <v>1</v>
-      </c>
-      <c r="L31" s="2">
-        <v>20</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N31" s="2">
-        <v>1</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="K31" s="3">
+        <v>30</v>
+      </c>
+      <c r="L31" s="3">
+        <v>1</v>
+      </c>
+      <c r="M31" s="3">
+        <v>30</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O31" s="2">
+        <v>1</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C32" s="2">
         <v>114</v>
       </c>
@@ -2379,40 +2495,44 @@
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
       </c>
       <c r="H32" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>170</v>
       </c>
       <c r="I32" s="2">
-        <v>2001</v>
+        <v>10</v>
       </c>
       <c r="J32" s="2">
-        <v>10</v>
+        <v>2002</v>
       </c>
       <c r="K32" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L32" s="2">
-        <v>10</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N32" s="2">
-        <v>1</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>1</v>
+      </c>
+      <c r="M32" s="2">
+        <v>25</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O32" s="2">
+        <v>1</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C33" s="2">
         <v>115</v>
       </c>
@@ -2420,40 +2540,44 @@
         <v>2</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>170</v>
       </c>
       <c r="I33" s="2">
-        <v>2001</v>
+        <v>10</v>
       </c>
       <c r="J33" s="2">
-        <v>10</v>
+        <v>2003</v>
       </c>
       <c r="K33" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L33" s="2">
-        <v>10</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N33" s="2">
-        <v>1</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>1</v>
+      </c>
+      <c r="M33" s="2">
+        <v>20</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O33" s="2">
+        <v>1</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C34" s="2">
         <v>116</v>
       </c>
@@ -2461,40 +2585,44 @@
         <v>2</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
       </c>
       <c r="H34" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>190</v>
       </c>
       <c r="I34" s="2">
+        <v>10</v>
+      </c>
+      <c r="J34" s="2">
         <v>2001</v>
       </c>
-      <c r="J34" s="2">
-        <v>10</v>
-      </c>
       <c r="K34" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L34" s="2">
-        <v>10</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N34" s="2">
-        <v>1</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>1</v>
+      </c>
+      <c r="M34" s="2">
+        <v>10</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O34" s="2">
+        <v>1</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C35" s="2">
         <v>117</v>
       </c>
@@ -2502,40 +2630,44 @@
         <v>2</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
       </c>
       <c r="H35" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>190</v>
       </c>
       <c r="I35" s="2">
+        <v>10</v>
+      </c>
+      <c r="J35" s="2">
         <v>2001</v>
       </c>
-      <c r="J35" s="2">
-        <v>1</v>
-      </c>
       <c r="K35" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L35" s="2">
         <v>1</v>
       </c>
-      <c r="M35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N35" s="2">
-        <v>1</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="M35" s="2">
+        <v>10</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O35" s="2">
+        <v>1</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C36" s="2">
         <v>118</v>
       </c>
@@ -2543,40 +2675,44 @@
         <v>2</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F36" s="2">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>190</v>
       </c>
       <c r="I36" s="2">
+        <v>10</v>
+      </c>
+      <c r="J36" s="2">
         <v>2001</v>
       </c>
-      <c r="J36" s="2">
-        <v>10</v>
-      </c>
       <c r="K36" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L36" s="2">
-        <v>10</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N36" s="2">
-        <v>1</v>
-      </c>
-      <c r="O36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M36" s="2">
+        <v>10</v>
+      </c>
+      <c r="N36" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O36" s="2">
+        <v>1</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C37" s="2">
         <v>119</v>
       </c>
@@ -2584,40 +2720,44 @@
         <v>2</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <v>10</v>
+        <f t="shared" ref="H37:H42" si="1">H34+20</f>
+        <v>210</v>
       </c>
       <c r="I37" s="2">
+        <v>10</v>
+      </c>
+      <c r="J37" s="2">
         <v>2001</v>
       </c>
-      <c r="J37" s="2">
-        <v>1</v>
-      </c>
       <c r="K37" s="2">
         <v>1</v>
       </c>
       <c r="L37" s="2">
         <v>1</v>
       </c>
-      <c r="M37" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N37" s="2">
-        <v>1</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:15">
+      <c r="M37" s="2">
+        <v>1</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O37" s="2">
+        <v>2</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C38" s="2">
         <v>120</v>
       </c>
@@ -2625,42 +2765,226 @@
         <v>2</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="2">
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>210</v>
       </c>
       <c r="I38" s="2">
+        <v>10</v>
+      </c>
+      <c r="J38" s="2">
         <v>2001</v>
       </c>
-      <c r="J38" s="2">
-        <v>1</v>
-      </c>
       <c r="K38" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L38" s="2">
         <v>1</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N38" s="2">
-        <v>1</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>54</v>
+      <c r="M38" s="2">
+        <v>10</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O38" s="2">
+        <v>2</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C39" s="2">
+        <v>121</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+      <c r="I39" s="2">
+        <v>10</v>
+      </c>
+      <c r="J39" s="2">
+        <v>2001</v>
+      </c>
+      <c r="K39" s="2">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2">
+        <v>1</v>
+      </c>
+      <c r="M39" s="2">
+        <v>1</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O39" s="2">
+        <v>2</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:16">
+      <c r="C40" s="2">
+        <v>122</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2">
+        <f t="shared" si="1"/>
+        <v>230</v>
+      </c>
+      <c r="I40" s="2">
+        <v>10</v>
+      </c>
+      <c r="J40" s="2">
+        <v>93</v>
+      </c>
+      <c r="K40" s="2">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2">
+        <v>1</v>
+      </c>
+      <c r="M40" s="2">
+        <v>1</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O40" s="2">
+        <v>3</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:16">
+      <c r="C41" s="2">
+        <v>123</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2">
+        <f t="shared" si="1"/>
+        <v>230</v>
+      </c>
+      <c r="I41" s="2">
+        <v>10</v>
+      </c>
+      <c r="J41" s="2">
+        <v>91</v>
+      </c>
+      <c r="K41" s="2">
+        <v>1</v>
+      </c>
+      <c r="L41" s="2">
+        <v>1</v>
+      </c>
+      <c r="M41" s="2">
+        <v>1</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O41" s="2">
+        <v>3</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:16">
+      <c r="C42" s="2">
+        <v>124</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2">
+        <f t="shared" si="1"/>
+        <v>230</v>
+      </c>
+      <c r="I42" s="2">
+        <v>10</v>
+      </c>
+      <c r="J42" s="2">
+        <v>92</v>
+      </c>
+      <c r="K42" s="2">
+        <v>1</v>
+      </c>
+      <c r="L42" s="2">
+        <v>1</v>
+      </c>
+      <c r="M42" s="2">
+        <v>1</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O42" s="2">
+        <v>3</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:O5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -476,12 +476,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1276,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
@@ -1928,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="J19" s="2">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="K19" s="2">
         <v>30</v>
@@ -2016,7 +2016,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="2">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="K21" s="2">
         <v>20</v>
@@ -2061,7 +2061,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="2">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="K22" s="2">
         <v>10</v>
@@ -2106,7 +2106,7 @@
         <v>10</v>
       </c>
       <c r="J23" s="2">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="K23" s="2">
         <v>10</v>
@@ -2151,7 +2151,7 @@
         <v>10</v>
       </c>
       <c r="J24" s="2">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="K24" s="2">
         <v>10</v>
@@ -2196,7 +2196,7 @@
         <v>10</v>
       </c>
       <c r="J25" s="2">
-        <v>2001</v>
+        <v>32</v>
       </c>
       <c r="K25" s="2">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>10</v>
       </c>
       <c r="J27" s="2">
-        <v>2001</v>
+        <v>31</v>
       </c>
       <c r="K27" s="2">
         <v>1</v>
@@ -2465,8 +2465,8 @@
       <c r="I31" s="3">
         <v>10</v>
       </c>
-      <c r="J31" s="3">
-        <v>2001</v>
+      <c r="J31" s="2">
+        <v>2003</v>
       </c>
       <c r="K31" s="3">
         <v>30</v>
@@ -2556,7 +2556,7 @@
         <v>10</v>
       </c>
       <c r="J33" s="2">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="K33" s="2">
         <v>20</v>
@@ -2601,7 +2601,7 @@
         <v>10</v>
       </c>
       <c r="J34" s="2">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="K34" s="2">
         <v>10</v>
@@ -2646,7 +2646,7 @@
         <v>10</v>
       </c>
       <c r="J35" s="2">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="K35" s="2">
         <v>10</v>
@@ -2691,7 +2691,7 @@
         <v>10</v>
       </c>
       <c r="J36" s="2">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="K36" s="2">
         <v>10</v>
@@ -2736,7 +2736,7 @@
         <v>10</v>
       </c>
       <c r="J37" s="2">
-        <v>2001</v>
+        <v>32</v>
       </c>
       <c r="K37" s="2">
         <v>1</v>
@@ -2826,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="J39" s="2">
-        <v>2001</v>
+        <v>31</v>
       </c>
       <c r="K39" s="2">
         <v>1</v>
@@ -2981,6 +2981,132 @@
       <c r="P42" s="2" t="s">
         <v>59</v>
       </c>
+    </row>
+    <row r="46" customHeight="1" spans="9:17">
+      <c r="I46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+    </row>
+    <row r="47" customHeight="1" spans="6:17">
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+    </row>
+    <row r="48" customHeight="1" spans="6:17">
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+    </row>
+    <row r="49" customHeight="1" spans="6:17">
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+    </row>
+    <row r="50" customHeight="1" spans="6:17">
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+    </row>
+    <row r="51" customHeight="1" spans="6:17">
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+    </row>
+    <row r="52" customHeight="1" spans="6:17">
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+    </row>
+    <row r="53" customHeight="1" spans="6:17">
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+    </row>
+    <row r="54" customHeight="1" spans="6:17">
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+    </row>
+    <row r="55" customHeight="1" spans="6:17">
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+    </row>
+    <row r="56" customHeight="1" spans="6:17">
+      <c r="F56" s="2"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+    </row>
+    <row r="57" customHeight="1" spans="6:17">
+      <c r="F57" s="2"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+    </row>
+    <row r="58" customHeight="1" spans="6:17">
+      <c r="F58" s="2"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+    </row>
+    <row r="59" customHeight="1" spans="9:17">
+      <c r="I59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+    </row>
+    <row r="60" customHeight="1" spans="9:17">
+      <c r="I60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+    </row>
+    <row r="61" customHeight="1" spans="9:17">
+      <c r="I61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+    </row>
+    <row r="62" customHeight="1" spans="9:17">
+      <c r="I62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+    </row>
+    <row r="63" customHeight="1" spans="9:17">
+      <c r="I63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="82">
   <si>
     <t>ID</t>
   </si>
@@ -206,30 +206,48 @@
     <t>生命·壹</t>
   </si>
   <si>
+    <t>生命</t>
+  </si>
+  <si>
     <t>防御·壹</t>
   </si>
   <si>
+    <t>防御</t>
+  </si>
+  <si>
     <t>韧性·壹</t>
   </si>
   <si>
+    <t>韧性</t>
+  </si>
+  <si>
     <t>提高韧性倍率{0}%</t>
   </si>
   <si>
     <t>物攻·壹</t>
   </si>
   <si>
+    <t>物攻</t>
+  </si>
+  <si>
     <t>提高物攻倍率{0}%</t>
   </si>
   <si>
     <t>魔攻·壹</t>
   </si>
   <si>
+    <t>魔攻</t>
+  </si>
+  <si>
     <t>提高魔法倍率{0}%</t>
   </si>
   <si>
     <t>道攻·壹</t>
   </si>
   <si>
+    <t>道攻</t>
+  </si>
+  <si>
     <t>提高道术倍率{0}%</t>
   </si>
   <si>
@@ -242,6 +260,9 @@
     <t>攻击·壹</t>
   </si>
   <si>
+    <t>攻击</t>
+  </si>
+  <si>
     <t>闪避·壹</t>
   </si>
   <si>
@@ -251,16 +272,25 @@
     <t>神命·壹</t>
   </si>
   <si>
+    <t>神命</t>
+  </si>
+  <si>
     <t>提高神话基础生命{0}%</t>
   </si>
   <si>
     <t>神攻·壹</t>
   </si>
   <si>
+    <t>神攻</t>
+  </si>
+  <si>
     <t>提高神话基础攻击{0}%</t>
   </si>
   <si>
     <t>神御·壹</t>
+  </si>
+  <si>
+    <t>神御</t>
   </si>
   <si>
     <t>提高神话基础防御{0}%</t>
@@ -476,12 +506,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1916,7 +1946,7 @@
         <v>39</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
@@ -1957,10 +1987,10 @@
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
@@ -2001,10 +2031,10 @@
         <v>2</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
@@ -2034,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2045,10 +2075,10 @@
         <v>2</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
@@ -2079,7 +2109,7 @@
         <v>1</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2090,10 +2120,10 @@
         <v>2</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
@@ -2124,7 +2154,7 @@
         <v>1</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2135,10 +2165,10 @@
         <v>2</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
@@ -2169,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2180,7 +2210,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>29</v>
@@ -2214,7 +2244,7 @@
         <v>2</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2225,10 +2255,10 @@
         <v>2</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
@@ -2270,7 +2300,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>24</v>
@@ -2304,7 +2334,7 @@
         <v>2</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2315,10 +2345,10 @@
         <v>2</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>33</v>
+        <v>61</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
@@ -2349,7 +2379,7 @@
         <v>3</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2360,10 +2390,10 @@
         <v>2</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>33</v>
+        <v>64</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
@@ -2394,7 +2424,7 @@
         <v>3</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2405,10 +2435,10 @@
         <v>2</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>33</v>
+        <v>67</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
@@ -2439,7 +2469,7 @@
         <v>3</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:16">
@@ -2450,10 +2480,10 @@
         <v>2</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>22</v>
+        <v>70</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="G31" s="3">
         <v>0</v>
@@ -2495,10 +2525,10 @@
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
@@ -2540,10 +2570,10 @@
         <v>2</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
@@ -2574,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2585,10 +2615,10 @@
         <v>2</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
@@ -2619,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2630,10 +2660,10 @@
         <v>2</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
@@ -2664,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2675,10 +2705,10 @@
         <v>2</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
@@ -2709,7 +2739,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2720,7 +2750,7 @@
         <v>2</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>29</v>
@@ -2754,7 +2784,7 @@
         <v>2</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2765,10 +2795,10 @@
         <v>2</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
@@ -2810,7 +2840,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>24</v>
@@ -2844,7 +2874,7 @@
         <v>2</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:16">
@@ -2855,10 +2885,10 @@
         <v>2</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>33</v>
+        <v>79</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
@@ -2889,7 +2919,7 @@
         <v>3</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:16">
@@ -2900,10 +2930,10 @@
         <v>2</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
@@ -2934,7 +2964,7 @@
         <v>3</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:16">
@@ -2945,10 +2975,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>33</v>
+        <v>81</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
@@ -2979,7 +3009,7 @@
         <v>3</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="9:17">
@@ -3061,7 +3091,6 @@
     </row>
     <row r="56" customHeight="1" spans="6:17">
       <c r="F56" s="2"/>
-      <c r="G56" s="1"/>
       <c r="H56" s="2"/>
       <c r="I56" s="4"/>
       <c r="P56" s="4"/>
@@ -3069,7 +3098,6 @@
     </row>
     <row r="57" customHeight="1" spans="6:17">
       <c r="F57" s="2"/>
-      <c r="G57" s="1"/>
       <c r="H57" s="2"/>
       <c r="I57" s="4"/>
       <c r="P57" s="4"/>
@@ -3077,7 +3105,6 @@
     </row>
     <row r="58" customHeight="1" spans="6:17">
       <c r="F58" s="2"/>
-      <c r="G58" s="1"/>
       <c r="H58" s="2"/>
       <c r="I58" s="4"/>
       <c r="P58" s="4"/>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="84">
   <si>
     <t>ID</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>溢出的减伤倍率，会额外计算</t>
+  </si>
+  <si>
+    <t>破敌</t>
+  </si>
+  <si>
+    <t>副本刷怪速度加快1倍</t>
   </si>
   <si>
     <t>生命·壹</t>
@@ -1932,7 +1938,47 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1"/>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C16" s="2">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>60</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1">
+        <v>107</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>15</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
     <row r="17" s="1" customFormat="1" customHeight="1"/>
     <row r="18" s="1" customFormat="1" customHeight="1"/>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -1943,10 +1989,10 @@
         <v>2</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
@@ -1987,10 +2033,10 @@
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
@@ -2031,10 +2077,10 @@
         <v>2</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
@@ -2064,7 +2110,7 @@
         <v>1</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2075,10 +2121,10 @@
         <v>2</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
@@ -2109,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2120,10 +2166,10 @@
         <v>2</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
@@ -2154,7 +2200,7 @@
         <v>1</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2165,10 +2211,10 @@
         <v>2</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
@@ -2199,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2210,7 +2256,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>29</v>
@@ -2244,7 +2290,7 @@
         <v>2</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2255,10 +2301,10 @@
         <v>2</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
@@ -2300,7 +2346,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>24</v>
@@ -2334,7 +2380,7 @@
         <v>2</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2345,10 +2391,10 @@
         <v>2</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G28" s="2">
         <v>0</v>
@@ -2379,7 +2425,7 @@
         <v>3</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2390,10 +2436,10 @@
         <v>2</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
@@ -2424,7 +2470,7 @@
         <v>3</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2435,10 +2481,10 @@
         <v>2</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
@@ -2469,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:16">
@@ -2480,10 +2526,10 @@
         <v>2</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G31" s="3">
         <v>0</v>
@@ -2525,10 +2571,10 @@
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
@@ -2570,10 +2616,10 @@
         <v>2</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
@@ -2604,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2615,10 +2661,10 @@
         <v>2</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
@@ -2649,7 +2695,7 @@
         <v>1</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2660,10 +2706,10 @@
         <v>2</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
@@ -2694,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2705,10 +2751,10 @@
         <v>2</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
@@ -2739,7 +2785,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2750,7 +2796,7 @@
         <v>2</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>29</v>
@@ -2784,7 +2830,7 @@
         <v>2</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2795,10 +2841,10 @@
         <v>2</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
@@ -2840,7 +2886,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>24</v>
@@ -2874,7 +2920,7 @@
         <v>2</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:16">
@@ -2885,10 +2931,10 @@
         <v>2</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
@@ -2919,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:16">
@@ -2930,10 +2976,10 @@
         <v>2</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
@@ -2964,7 +3010,7 @@
         <v>3</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:16">
@@ -2975,10 +3021,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
@@ -3009,7 +3055,7 @@
         <v>3</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="9:17">

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>40</v>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="112">
   <si>
     <t>ID</t>
   </si>
@@ -336,6 +336,90 @@
   </si>
   <si>
     <t>神御·贰</t>
+  </si>
+  <si>
+    <t>经验·壹</t>
+  </si>
+  <si>
+    <t>经验</t>
+  </si>
+  <si>
+    <t>提高经验加成{0}%</t>
+  </si>
+  <si>
+    <t>金币·壹</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>提高金币加成{0}%</t>
+  </si>
+  <si>
+    <t>爆率·壹</t>
+  </si>
+  <si>
+    <t>爆率</t>
+  </si>
+  <si>
+    <t>提高爆率加成{0}%</t>
+  </si>
+  <si>
+    <t>品质·壹</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>提高品质加成{0}%</t>
+  </si>
+  <si>
+    <t>经验增幅</t>
+  </si>
+  <si>
+    <t>提高经验增幅{0}%</t>
+  </si>
+  <si>
+    <t>增伤·壹</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>提高增伤倍率{0}%</t>
+  </si>
+  <si>
+    <t>金币增幅</t>
+  </si>
+  <si>
+    <t>提高金币增幅{0}%</t>
+  </si>
+  <si>
+    <t>经验·贰</t>
+  </si>
+  <si>
+    <t>金币·贰</t>
+  </si>
+  <si>
+    <t>爆率·贰</t>
+  </si>
+  <si>
+    <t>品质·贰</t>
+  </si>
+  <si>
+    <t>爆率增幅</t>
+  </si>
+  <si>
+    <t>提高爆率增幅{0}%</t>
+  </si>
+  <si>
+    <t>增伤·贰</t>
+  </si>
+  <si>
+    <t>品质增幅</t>
+  </si>
+  <si>
+    <t>提高品质增幅{0}%</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1396,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S63"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
@@ -1501,7 +1585,7 @@
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:19">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1545,7 +1629,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:19">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1589,7 +1673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:19">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1633,7 +1717,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:19">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1677,7 +1761,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:19">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1721,7 +1805,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="C11" s="2">
         <v>6</v>
       </c>
@@ -1765,7 +1849,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -1809,7 +1893,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -1853,7 +1937,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -1897,7 +1981,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -1938,7 +2022,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="C16" s="2">
         <v>11</v>
       </c>
@@ -2608,7 +2692,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C33" s="2">
         <v>115</v>
       </c>
@@ -2653,7 +2737,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C34" s="2">
         <v>116</v>
       </c>
@@ -2698,7 +2782,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C35" s="2">
         <v>117</v>
       </c>
@@ -2743,7 +2827,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C36" s="2">
         <v>118</v>
       </c>
@@ -2788,7 +2872,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C37" s="2">
         <v>119</v>
       </c>
@@ -2833,7 +2917,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C38" s="2">
         <v>120</v>
       </c>
@@ -2878,7 +2962,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:17">
       <c r="C39" s="2">
         <v>121</v>
       </c>
@@ -2923,7 +3007,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:16">
+    <row r="40" customHeight="1" spans="3:17">
       <c r="C40" s="2">
         <v>122</v>
       </c>
@@ -2968,7 +3052,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:16">
+    <row r="41" customHeight="1" spans="3:17">
       <c r="C41" s="2">
         <v>123</v>
       </c>
@@ -3013,7 +3097,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:16">
+    <row r="42" customHeight="1" spans="3:17">
       <c r="C42" s="2">
         <v>124</v>
       </c>
@@ -3058,128 +3142,1103 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="9:17">
-      <c r="I46" s="4"/>
-      <c r="P46" s="4"/>
+    <row r="44" customHeight="1" spans="3:17">
+      <c r="C44" s="2">
+        <v>201</v>
+      </c>
+      <c r="D44" s="2">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2">
+        <f t="shared" ref="H44:H67" si="2">H19+100</f>
+        <v>190</v>
+      </c>
+      <c r="I44" s="2">
+        <v>20</v>
+      </c>
+      <c r="J44" s="2">
+        <v>18</v>
+      </c>
+      <c r="K44" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L44" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M44" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O44" s="2">
+        <v>1</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:17">
+      <c r="C45" s="2">
+        <v>202</v>
+      </c>
+      <c r="D45" s="2">
+        <v>3</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+      <c r="I45" s="2">
+        <v>10</v>
+      </c>
+      <c r="J45" s="2">
+        <v>2001</v>
+      </c>
+      <c r="K45" s="2">
+        <v>10</v>
+      </c>
+      <c r="L45" s="2">
+        <v>10</v>
+      </c>
+      <c r="M45" s="2">
+        <v>10</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O45" s="2">
+        <v>1</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:17">
+      <c r="C46" s="2">
+        <v>203</v>
+      </c>
+      <c r="D46" s="2">
+        <v>3</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+      <c r="I46" s="2">
+        <v>20</v>
+      </c>
+      <c r="J46" s="2">
+        <v>20</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L46" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M46" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O46" s="2">
+        <v>1</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" customHeight="1" spans="6:17">
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="4"/>
-      <c r="P47" s="4"/>
+    <row r="47" customHeight="1" spans="3:17">
+      <c r="C47" s="2">
+        <v>204</v>
+      </c>
+      <c r="D47" s="2">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G47" s="2">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+      <c r="I47" s="2">
+        <v>20</v>
+      </c>
+      <c r="J47" s="2">
+        <v>19</v>
+      </c>
+      <c r="K47" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L47" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M47" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O47" s="2">
+        <v>1</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" customHeight="1" spans="6:17">
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="4"/>
-      <c r="P48" s="4"/>
+    <row r="48" customHeight="1" spans="3:17">
+      <c r="C48" s="2">
+        <v>205</v>
+      </c>
+      <c r="D48" s="2">
+        <v>3</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+      <c r="I48" s="2">
+        <v>10</v>
+      </c>
+      <c r="J48" s="2">
+        <v>2004</v>
+      </c>
+      <c r="K48" s="2">
+        <v>20</v>
+      </c>
+      <c r="L48" s="2">
+        <v>20</v>
+      </c>
+      <c r="M48" s="2">
+        <v>20</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O48" s="2">
+        <v>1</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" customHeight="1" spans="6:17">
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="4"/>
-      <c r="P49" s="4"/>
+    <row r="49" customHeight="1" spans="3:17">
+      <c r="C49" s="2">
+        <v>206</v>
+      </c>
+      <c r="D49" s="2">
+        <v>3</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+      <c r="I49" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" s="2">
+        <v>24</v>
+      </c>
+      <c r="K49" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L49" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M49" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O49" s="2">
+        <v>1</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" customHeight="1" spans="6:17">
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="4"/>
-      <c r="P50" s="4"/>
+    <row r="50" customHeight="1" spans="3:17">
+      <c r="C50" s="2">
+        <v>207</v>
+      </c>
+      <c r="D50" s="2">
+        <v>3</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2">
+        <f t="shared" si="2"/>
+        <v>230</v>
+      </c>
+      <c r="I50" s="2">
+        <v>10</v>
+      </c>
+      <c r="J50" s="2">
+        <v>50</v>
+      </c>
+      <c r="K50" s="2">
+        <v>1</v>
+      </c>
+      <c r="L50" s="2">
+        <v>1</v>
+      </c>
+      <c r="M50" s="2">
+        <v>1</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O50" s="2">
+        <v>3</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" customHeight="1" spans="6:17">
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="4"/>
-      <c r="P51" s="4"/>
+    <row r="51" customHeight="1" spans="3:17">
+      <c r="C51" s="2">
+        <v>208</v>
+      </c>
+      <c r="D51" s="2">
+        <v>3</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2">
+        <f t="shared" si="2"/>
+        <v>230</v>
+      </c>
+      <c r="I51" s="2">
+        <v>10</v>
+      </c>
+      <c r="J51" s="2">
+        <v>2001</v>
+      </c>
+      <c r="K51" s="2">
+        <v>10</v>
+      </c>
+      <c r="L51" s="2">
+        <v>10</v>
+      </c>
+      <c r="M51" s="2">
+        <v>10</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O51" s="2">
+        <v>1</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" customHeight="1" spans="6:17">
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="4"/>
-      <c r="P52" s="4"/>
+    <row r="52" customHeight="1" spans="3:17">
+      <c r="C52" s="2">
+        <v>209</v>
+      </c>
+      <c r="D52" s="2">
+        <v>3</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G52" s="2">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2">
+        <f t="shared" si="2"/>
+        <v>230</v>
+      </c>
+      <c r="I52" s="2">
+        <v>10</v>
+      </c>
+      <c r="J52" s="2">
+        <v>51</v>
+      </c>
+      <c r="K52" s="2">
+        <v>1</v>
+      </c>
+      <c r="L52" s="2">
+        <v>1</v>
+      </c>
+      <c r="M52" s="2">
+        <v>1</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O52" s="2">
+        <v>3</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" customHeight="1" spans="6:17">
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="4"/>
-      <c r="P53" s="4"/>
+    <row r="53" customHeight="1" spans="3:17">
+      <c r="C53" s="2">
+        <v>210</v>
+      </c>
+      <c r="D53" s="2">
+        <v>3</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G53" s="2">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+      <c r="I53" s="2">
+        <v>10</v>
+      </c>
+      <c r="J53" s="2">
+        <v>93</v>
+      </c>
+      <c r="K53" s="2">
+        <v>1</v>
+      </c>
+      <c r="L53" s="2">
+        <v>1</v>
+      </c>
+      <c r="M53" s="2">
+        <v>1</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O53" s="2">
+        <v>3</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" customHeight="1" spans="6:17">
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="4"/>
-      <c r="P54" s="4"/>
+    <row r="54" customHeight="1" spans="3:17">
+      <c r="C54" s="2">
+        <v>211</v>
+      </c>
+      <c r="D54" s="2">
+        <v>3</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G54" s="2">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+      <c r="I54" s="2">
+        <v>10</v>
+      </c>
+      <c r="J54" s="2">
+        <v>91</v>
+      </c>
+      <c r="K54" s="2">
+        <v>1</v>
+      </c>
+      <c r="L54" s="2">
+        <v>1</v>
+      </c>
+      <c r="M54" s="2">
+        <v>1</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O54" s="2">
+        <v>3</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" customHeight="1" spans="6:17">
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="4"/>
-      <c r="P55" s="4"/>
+    <row r="55" customHeight="1" spans="3:17">
+      <c r="C55" s="2">
+        <v>212</v>
+      </c>
+      <c r="D55" s="2">
+        <v>3</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G55" s="2">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+      <c r="I55" s="2">
+        <v>10</v>
+      </c>
+      <c r="J55" s="2">
+        <v>92</v>
+      </c>
+      <c r="K55" s="2">
+        <v>1</v>
+      </c>
+      <c r="L55" s="2">
+        <v>1</v>
+      </c>
+      <c r="M55" s="2">
+        <v>1</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O55" s="2">
+        <v>3</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" customHeight="1" spans="6:17">
-      <c r="F56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="4"/>
-      <c r="P56" s="4"/>
+    <row r="56" customHeight="1" spans="3:17">
+      <c r="C56" s="2">
+        <v>213</v>
+      </c>
+      <c r="D56" s="2">
+        <v>3</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2">
+        <f t="shared" si="2"/>
+        <v>270</v>
+      </c>
+      <c r="I56" s="2">
+        <v>20</v>
+      </c>
+      <c r="J56" s="2">
+        <v>18</v>
+      </c>
+      <c r="K56" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L56" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M56" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O56" s="2">
+        <v>1</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" customHeight="1" spans="6:17">
-      <c r="F57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="4"/>
-      <c r="P57" s="4"/>
+    <row r="57" customHeight="1" spans="3:17">
+      <c r="C57" s="2">
+        <v>214</v>
+      </c>
+      <c r="D57" s="2">
+        <v>3</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G57" s="2">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2">
+        <f t="shared" si="2"/>
+        <v>270</v>
+      </c>
+      <c r="I57" s="2">
+        <v>10</v>
+      </c>
+      <c r="J57" s="2">
+        <v>2001</v>
+      </c>
+      <c r="K57" s="2">
+        <v>10</v>
+      </c>
+      <c r="L57" s="2">
+        <v>10</v>
+      </c>
+      <c r="M57" s="2">
+        <v>10</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O57" s="2">
+        <v>1</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" customHeight="1" spans="6:17">
-      <c r="F58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="4"/>
-      <c r="P58" s="4"/>
+    <row r="58" customHeight="1" spans="3:17">
+      <c r="C58" s="2">
+        <v>215</v>
+      </c>
+      <c r="D58" s="2">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G58" s="2">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="2"/>
+        <v>270</v>
+      </c>
+      <c r="I58" s="2">
+        <v>20</v>
+      </c>
+      <c r="J58" s="2">
+        <v>20</v>
+      </c>
+      <c r="K58" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L58" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M58" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O58" s="2">
+        <v>1</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="Q58" s="4"/>
     </row>
-    <row r="59" customHeight="1" spans="9:17">
-      <c r="I59" s="4"/>
-      <c r="P59" s="4"/>
+    <row r="59" customHeight="1" spans="3:17">
+      <c r="C59" s="2">
+        <v>216</v>
+      </c>
+      <c r="D59" s="2">
+        <v>3</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G59" s="2">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2">
+        <f t="shared" si="2"/>
+        <v>290</v>
+      </c>
+      <c r="I59" s="2">
+        <v>20</v>
+      </c>
+      <c r="J59" s="2">
+        <v>19</v>
+      </c>
+      <c r="K59" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L59" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M59" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O59" s="2">
+        <v>1</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" customHeight="1" spans="9:17">
-      <c r="I60" s="4"/>
-      <c r="P60" s="4"/>
+    <row r="60" customHeight="1" spans="3:17">
+      <c r="C60" s="2">
+        <v>217</v>
+      </c>
+      <c r="D60" s="2">
+        <v>3</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" s="2">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2">
+        <f t="shared" si="2"/>
+        <v>290</v>
+      </c>
+      <c r="I60" s="2">
+        <v>10</v>
+      </c>
+      <c r="J60" s="2">
+        <v>2004</v>
+      </c>
+      <c r="K60" s="2">
+        <v>20</v>
+      </c>
+      <c r="L60" s="2">
+        <v>20</v>
+      </c>
+      <c r="M60" s="2">
+        <v>20</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O60" s="2">
+        <v>1</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" customHeight="1" spans="9:17">
-      <c r="I61" s="4"/>
-      <c r="P61" s="4"/>
+    <row r="61" customHeight="1" spans="3:17">
+      <c r="C61" s="2">
+        <v>218</v>
+      </c>
+      <c r="D61" s="2">
+        <v>3</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G61" s="2">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2">
+        <f t="shared" si="2"/>
+        <v>290</v>
+      </c>
+      <c r="I61" s="2">
+        <v>20</v>
+      </c>
+      <c r="J61" s="2">
+        <v>24</v>
+      </c>
+      <c r="K61" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L61" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M61" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O61" s="2">
+        <v>1</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" customHeight="1" spans="9:17">
-      <c r="I62" s="4"/>
-      <c r="P62" s="4"/>
+    <row r="62" customHeight="1" spans="3:17">
+      <c r="C62" s="2">
+        <v>219</v>
+      </c>
+      <c r="D62" s="2">
+        <v>3</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G62" s="2">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2">
+        <f t="shared" si="2"/>
+        <v>310</v>
+      </c>
+      <c r="I62" s="2">
+        <v>10</v>
+      </c>
+      <c r="J62" s="2">
+        <v>52</v>
+      </c>
+      <c r="K62" s="2">
+        <v>1</v>
+      </c>
+      <c r="L62" s="2">
+        <v>1</v>
+      </c>
+      <c r="M62" s="2">
+        <v>1</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O62" s="2">
+        <v>3</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="Q62" s="4"/>
     </row>
-    <row r="63" customHeight="1" spans="9:17">
-      <c r="I63" s="4"/>
-      <c r="P63" s="4"/>
+    <row r="63" customHeight="1" spans="3:17">
+      <c r="C63" s="2">
+        <v>220</v>
+      </c>
+      <c r="D63" s="2">
+        <v>3</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G63" s="2">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2">
+        <f t="shared" si="2"/>
+        <v>310</v>
+      </c>
+      <c r="I63" s="2">
+        <v>10</v>
+      </c>
+      <c r="J63" s="2">
+        <v>2001</v>
+      </c>
+      <c r="K63" s="2">
+        <v>10</v>
+      </c>
+      <c r="L63" s="2">
+        <v>10</v>
+      </c>
+      <c r="M63" s="2">
+        <v>10</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O63" s="2">
+        <v>1</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="Q63" s="4"/>
+    </row>
+    <row r="64" customHeight="1" spans="3:17">
+      <c r="C64" s="2">
+        <v>221</v>
+      </c>
+      <c r="D64" s="2">
+        <v>3</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G64" s="2">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2">
+        <f t="shared" si="2"/>
+        <v>310</v>
+      </c>
+      <c r="I64" s="2">
+        <v>10</v>
+      </c>
+      <c r="J64" s="2">
+        <v>53</v>
+      </c>
+      <c r="K64" s="2">
+        <v>1</v>
+      </c>
+      <c r="L64" s="2">
+        <v>1</v>
+      </c>
+      <c r="M64" s="2">
+        <v>1</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O64" s="2">
+        <v>3</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:16">
+      <c r="C65" s="2">
+        <v>222</v>
+      </c>
+      <c r="D65" s="2">
+        <v>3</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G65" s="2">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2">
+        <f t="shared" si="2"/>
+        <v>330</v>
+      </c>
+      <c r="I65" s="2">
+        <v>10</v>
+      </c>
+      <c r="J65" s="2">
+        <v>93</v>
+      </c>
+      <c r="K65" s="2">
+        <v>1</v>
+      </c>
+      <c r="L65" s="2">
+        <v>1</v>
+      </c>
+      <c r="M65" s="2">
+        <v>1</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O65" s="2">
+        <v>3</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:16">
+      <c r="C66" s="2">
+        <v>223</v>
+      </c>
+      <c r="D66" s="2">
+        <v>3</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G66" s="2">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2">
+        <f t="shared" si="2"/>
+        <v>330</v>
+      </c>
+      <c r="I66" s="2">
+        <v>10</v>
+      </c>
+      <c r="J66" s="2">
+        <v>91</v>
+      </c>
+      <c r="K66" s="2">
+        <v>1</v>
+      </c>
+      <c r="L66" s="2">
+        <v>1</v>
+      </c>
+      <c r="M66" s="2">
+        <v>1</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O66" s="2">
+        <v>3</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:16">
+      <c r="C67" s="2">
+        <v>224</v>
+      </c>
+      <c r="D67" s="2">
+        <v>3</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2">
+        <f t="shared" si="2"/>
+        <v>330</v>
+      </c>
+      <c r="I67" s="2">
+        <v>10</v>
+      </c>
+      <c r="J67" s="2">
+        <v>92</v>
+      </c>
+      <c r="K67" s="2">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2">
+        <v>1</v>
+      </c>
+      <c r="M67" s="2">
+        <v>1</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O67" s="2">
+        <v>3</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="111">
   <si>
     <t>ID</t>
   </si>
@@ -381,9 +381,6 @@
   </si>
   <si>
     <t>增伤·壹</t>
-  </si>
-  <si>
-    <t>增伤</t>
   </si>
   <si>
     <t>提高增伤倍率{0}%</t>
@@ -3172,7 +3169,7 @@
         <v>1000</v>
       </c>
       <c r="L44" s="2">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2">
         <v>1000</v>
@@ -3217,7 +3214,7 @@
         <v>10</v>
       </c>
       <c r="L45" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2">
         <v>10</v>
@@ -3262,7 +3259,7 @@
         <v>1000</v>
       </c>
       <c r="L46" s="2">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2">
         <v>1000</v>
@@ -3308,7 +3305,7 @@
         <v>1000</v>
       </c>
       <c r="L47" s="2">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2">
         <v>1000</v>
@@ -3354,7 +3351,7 @@
         <v>20</v>
       </c>
       <c r="L48" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2">
         <v>20</v>
@@ -3400,7 +3397,7 @@
         <v>1000</v>
       </c>
       <c r="L49" s="2">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2">
         <v>1000</v>
@@ -3472,8 +3469,8 @@
       <c r="E51" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>99</v>
+      <c r="F51" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
@@ -3492,7 +3489,7 @@
         <v>10</v>
       </c>
       <c r="L51" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2">
         <v>10</v>
@@ -3504,7 +3501,7 @@
         <v>1</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q51" s="4"/>
     </row>
@@ -3516,10 +3513,10 @@
         <v>3</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
@@ -3550,7 +3547,7 @@
         <v>3</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q52" s="4"/>
     </row>
@@ -3700,7 +3697,7 @@
         <v>3</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>85</v>
@@ -3722,7 +3719,7 @@
         <v>1000</v>
       </c>
       <c r="L56" s="2">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2">
         <v>1000</v>
@@ -3768,7 +3765,7 @@
         <v>10</v>
       </c>
       <c r="L57" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2">
         <v>10</v>
@@ -3792,7 +3789,7 @@
         <v>3</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>88</v>
@@ -3814,7 +3811,7 @@
         <v>1000</v>
       </c>
       <c r="L58" s="2">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2">
         <v>1000</v>
@@ -3838,7 +3835,7 @@
         <v>3</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>91</v>
@@ -3860,7 +3857,7 @@
         <v>1000</v>
       </c>
       <c r="L59" s="2">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2">
         <v>1000</v>
@@ -3906,7 +3903,7 @@
         <v>20</v>
       </c>
       <c r="L60" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2">
         <v>20</v>
@@ -3930,7 +3927,7 @@
         <v>3</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>94</v>
@@ -3952,7 +3949,7 @@
         <v>1000</v>
       </c>
       <c r="L61" s="2">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2">
         <v>1000</v>
@@ -3976,10 +3973,10 @@
         <v>3</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
@@ -4010,7 +4007,7 @@
         <v>3</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q62" s="4"/>
     </row>
@@ -4022,10 +4019,10 @@
         <v>3</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
@@ -4044,7 +4041,7 @@
         <v>10</v>
       </c>
       <c r="L63" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2">
         <v>10</v>
@@ -4056,7 +4053,7 @@
         <v>1</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q63" s="4"/>
     </row>
@@ -4068,10 +4065,10 @@
         <v>3</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G64" s="2">
         <v>0</v>
@@ -4102,7 +4099,7 @@
         <v>3</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:16">

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -593,12 +593,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3345,7 +3345,7 @@
         <v>10</v>
       </c>
       <c r="J48" s="2">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="K48" s="2">
         <v>20</v>
@@ -3897,7 +3897,7 @@
         <v>10</v>
       </c>
       <c r="J60" s="2">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="K60" s="2">
         <v>20</v>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -206,7 +206,7 @@
     <t>破敌</t>
   </si>
   <si>
-    <t>副本刷怪速度加快1倍</t>
+    <t>副本刷怪速度加快{0}倍</t>
   </si>
   <si>
     <t>生命·壹</t>
@@ -593,12 +593,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2039,7 +2039,7 @@
         <v>60</v>
       </c>
       <c r="I16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="1">
         <v>107</v>
@@ -2051,7 +2051,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="1">
         <v>20</v>

--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -417,6 +417,30 @@
   </si>
   <si>
     <t>提高品质增幅{0}%</t>
+  </si>
+  <si>
+    <t>破韧·壹</t>
+  </si>
+  <si>
+    <t>提高破韧倍率{0}%</t>
+  </si>
+  <si>
+    <t>物伤·壹</t>
+  </si>
+  <si>
+    <t>提高物伤倍率{0}%</t>
+  </si>
+  <si>
+    <t>魔伤·壹</t>
+  </si>
+  <si>
+    <t>提高魔伤倍率{0}%</t>
+  </si>
+  <si>
+    <t>道伤·壹</t>
+  </si>
+  <si>
+    <t>提高道伤倍率{0}%</t>
   </si>
 </sst>
 </file>
@@ -1393,7 +1417,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S67"/>
+  <dimension ref="A1:S92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
@@ -4237,6 +4261,1083 @@
         <v>71</v>
       </c>
     </row>
+    <row r="69" customHeight="1" spans="3:16">
+      <c r="C69" s="2">
+        <v>301</v>
+      </c>
+      <c r="D69" s="2">
+        <v>2</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69" s="2">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2">
+        <v>290</v>
+      </c>
+      <c r="I69" s="2">
+        <v>20</v>
+      </c>
+      <c r="J69" s="2">
+        <v>2003</v>
+      </c>
+      <c r="K69" s="2">
+        <v>50</v>
+      </c>
+      <c r="L69" s="2">
+        <v>1</v>
+      </c>
+      <c r="M69" s="2">
+        <v>50</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O69" s="2">
+        <v>2</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:16">
+      <c r="C70" s="2">
+        <v>302</v>
+      </c>
+      <c r="D70" s="2">
+        <v>2</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="2">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2">
+        <v>290</v>
+      </c>
+      <c r="I70" s="2">
+        <v>20</v>
+      </c>
+      <c r="J70" s="2">
+        <v>2013</v>
+      </c>
+      <c r="K70" s="2">
+        <v>20</v>
+      </c>
+      <c r="L70" s="2">
+        <v>1</v>
+      </c>
+      <c r="M70" s="2">
+        <v>20</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O70" s="2">
+        <v>2</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:16">
+      <c r="C71" s="2">
+        <v>303</v>
+      </c>
+      <c r="D71" s="2">
+        <v>2</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G71" s="2">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2">
+        <v>290</v>
+      </c>
+      <c r="I71" s="2">
+        <v>20</v>
+      </c>
+      <c r="J71" s="2">
+        <v>2012</v>
+      </c>
+      <c r="K71" s="2">
+        <v>50</v>
+      </c>
+      <c r="L71" s="2">
+        <v>1</v>
+      </c>
+      <c r="M71" s="2">
+        <v>50</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O71" s="2">
+        <v>2</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:16">
+      <c r="C72" s="2">
+        <v>304</v>
+      </c>
+      <c r="D72" s="2">
+        <v>2</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G72" s="2">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2">
+        <f t="shared" ref="H72:H80" si="3">H69+20</f>
+        <v>310</v>
+      </c>
+      <c r="I72" s="2">
+        <v>20</v>
+      </c>
+      <c r="J72" s="2">
+        <v>2007</v>
+      </c>
+      <c r="K72" s="2">
+        <v>20</v>
+      </c>
+      <c r="L72" s="2">
+        <v>1</v>
+      </c>
+      <c r="M72" s="2">
+        <v>20</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O72" s="2">
+        <v>2</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:16">
+      <c r="C73" s="2">
+        <v>305</v>
+      </c>
+      <c r="D73" s="2">
+        <v>2</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G73" s="2">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2">
+        <f t="shared" si="3"/>
+        <v>310</v>
+      </c>
+      <c r="I73" s="2">
+        <v>20</v>
+      </c>
+      <c r="J73" s="2">
+        <v>2008</v>
+      </c>
+      <c r="K73" s="2">
+        <v>20</v>
+      </c>
+      <c r="L73" s="2">
+        <v>1</v>
+      </c>
+      <c r="M73" s="2">
+        <v>20</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O73" s="2">
+        <v>2</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:16">
+      <c r="C74" s="2">
+        <v>306</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G74" s="2">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2">
+        <f t="shared" si="3"/>
+        <v>310</v>
+      </c>
+      <c r="I74" s="2">
+        <v>20</v>
+      </c>
+      <c r="J74" s="2">
+        <v>2009</v>
+      </c>
+      <c r="K74" s="2">
+        <v>20</v>
+      </c>
+      <c r="L74" s="2">
+        <v>1</v>
+      </c>
+      <c r="M74" s="2">
+        <v>20</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O74" s="2">
+        <v>2</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:16">
+      <c r="C75" s="2">
+        <v>307</v>
+      </c>
+      <c r="D75" s="2">
+        <v>2</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G75" s="2">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2">
+        <f t="shared" si="3"/>
+        <v>330</v>
+      </c>
+      <c r="I75" s="2">
+        <v>20</v>
+      </c>
+      <c r="J75" s="2">
+        <v>32</v>
+      </c>
+      <c r="K75" s="2">
+        <v>2</v>
+      </c>
+      <c r="L75" s="2">
+        <v>1</v>
+      </c>
+      <c r="M75" s="2">
+        <v>2</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O75" s="2">
+        <v>4</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:16">
+      <c r="C76" s="2">
+        <v>308</v>
+      </c>
+      <c r="D76" s="2">
+        <v>2</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G76" s="2">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2">
+        <f t="shared" si="3"/>
+        <v>330</v>
+      </c>
+      <c r="I76" s="2">
+        <v>20</v>
+      </c>
+      <c r="J76" s="2">
+        <v>2001</v>
+      </c>
+      <c r="K76" s="2">
+        <v>20</v>
+      </c>
+      <c r="L76" s="2">
+        <v>1</v>
+      </c>
+      <c r="M76" s="2">
+        <v>20</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O76" s="2">
+        <v>4</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:16">
+      <c r="C77" s="2">
+        <v>309</v>
+      </c>
+      <c r="D77" s="2">
+        <v>2</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G77" s="2">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2">
+        <f t="shared" si="3"/>
+        <v>330</v>
+      </c>
+      <c r="I77" s="2">
+        <v>20</v>
+      </c>
+      <c r="J77" s="2">
+        <v>31</v>
+      </c>
+      <c r="K77" s="2">
+        <v>2</v>
+      </c>
+      <c r="L77" s="2">
+        <v>1</v>
+      </c>
+      <c r="M77" s="2">
+        <v>2</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O77" s="2">
+        <v>4</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:16">
+      <c r="C78" s="2">
+        <v>310</v>
+      </c>
+      <c r="D78" s="2">
+        <v>2</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G78" s="2">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+      <c r="I78" s="2">
+        <v>10</v>
+      </c>
+      <c r="J78" s="2">
+        <v>93</v>
+      </c>
+      <c r="K78" s="2">
+        <v>2</v>
+      </c>
+      <c r="L78" s="2">
+        <v>1</v>
+      </c>
+      <c r="M78" s="2">
+        <v>2</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O78" s="2">
+        <v>6</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:16">
+      <c r="C79" s="2">
+        <v>311</v>
+      </c>
+      <c r="D79" s="2">
+        <v>2</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G79" s="2">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+      <c r="I79" s="2">
+        <v>10</v>
+      </c>
+      <c r="J79" s="2">
+        <v>91</v>
+      </c>
+      <c r="K79" s="2">
+        <v>2</v>
+      </c>
+      <c r="L79" s="2">
+        <v>1</v>
+      </c>
+      <c r="M79" s="2">
+        <v>2</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O79" s="2">
+        <v>6</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:16">
+      <c r="C80" s="2">
+        <v>312</v>
+      </c>
+      <c r="D80" s="2">
+        <v>2</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G80" s="2">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2">
+        <f t="shared" si="3"/>
+        <v>350</v>
+      </c>
+      <c r="I80" s="2">
+        <v>10</v>
+      </c>
+      <c r="J80" s="2">
+        <v>92</v>
+      </c>
+      <c r="K80" s="2">
+        <v>2</v>
+      </c>
+      <c r="L80" s="2">
+        <v>1</v>
+      </c>
+      <c r="M80" s="2">
+        <v>2</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O80" s="2">
+        <v>6</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:16">
+      <c r="C81" s="2">
+        <v>313</v>
+      </c>
+      <c r="D81" s="3">
+        <v>2</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G81" s="2">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2">
+        <f t="shared" ref="H81:H92" si="4">H56+100</f>
+        <v>370</v>
+      </c>
+      <c r="I81" s="2">
+        <v>20</v>
+      </c>
+      <c r="J81" s="2">
+        <v>2003</v>
+      </c>
+      <c r="K81" s="2">
+        <v>50</v>
+      </c>
+      <c r="L81" s="2">
+        <v>1</v>
+      </c>
+      <c r="M81" s="2">
+        <v>50</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O81" s="2">
+        <v>2</v>
+      </c>
+      <c r="P81" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:16">
+      <c r="C82" s="2">
+        <v>314</v>
+      </c>
+      <c r="D82" s="2">
+        <v>2</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="2">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2">
+        <f t="shared" si="4"/>
+        <v>370</v>
+      </c>
+      <c r="I82" s="2">
+        <v>20</v>
+      </c>
+      <c r="J82" s="2">
+        <v>2013</v>
+      </c>
+      <c r="K82" s="2">
+        <v>20</v>
+      </c>
+      <c r="L82" s="2">
+        <v>1</v>
+      </c>
+      <c r="M82" s="2">
+        <v>20</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O82" s="2">
+        <v>2</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:16">
+      <c r="C83" s="2">
+        <v>315</v>
+      </c>
+      <c r="D83" s="2">
+        <v>2</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G83" s="2">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2">
+        <f t="shared" si="4"/>
+        <v>370</v>
+      </c>
+      <c r="I83" s="2">
+        <v>20</v>
+      </c>
+      <c r="J83" s="2">
+        <v>2012</v>
+      </c>
+      <c r="K83" s="2">
+        <v>50</v>
+      </c>
+      <c r="L83" s="2">
+        <v>1</v>
+      </c>
+      <c r="M83" s="2">
+        <v>50</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O83" s="2">
+        <v>2</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:16">
+      <c r="C84" s="2">
+        <v>316</v>
+      </c>
+      <c r="D84" s="2">
+        <v>2</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G84" s="2">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2">
+        <f t="shared" si="4"/>
+        <v>390</v>
+      </c>
+      <c r="I84" s="2">
+        <v>20</v>
+      </c>
+      <c r="J84" s="2">
+        <v>2007</v>
+      </c>
+      <c r="K84" s="2">
+        <v>20</v>
+      </c>
+      <c r="L84" s="2">
+        <v>1</v>
+      </c>
+      <c r="M84" s="2">
+        <v>20</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O84" s="2">
+        <v>2</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:16">
+      <c r="C85" s="2">
+        <v>317</v>
+      </c>
+      <c r="D85" s="2">
+        <v>2</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G85" s="2">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2">
+        <f t="shared" si="4"/>
+        <v>390</v>
+      </c>
+      <c r="I85" s="2">
+        <v>20</v>
+      </c>
+      <c r="J85" s="2">
+        <v>2008</v>
+      </c>
+      <c r="K85" s="2">
+        <v>20</v>
+      </c>
+      <c r="L85" s="2">
+        <v>1</v>
+      </c>
+      <c r="M85" s="2">
+        <v>20</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O85" s="2">
+        <v>2</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:16">
+      <c r="C86" s="2">
+        <v>318</v>
+      </c>
+      <c r="D86" s="2">
+        <v>2</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G86" s="2">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2">
+        <f t="shared" si="4"/>
+        <v>390</v>
+      </c>
+      <c r="I86" s="2">
+        <v>20</v>
+      </c>
+      <c r="J86" s="2">
+        <v>2009</v>
+      </c>
+      <c r="K86" s="2">
+        <v>20</v>
+      </c>
+      <c r="L86" s="2">
+        <v>1</v>
+      </c>
+      <c r="M86" s="2">
+        <v>20</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O86" s="2">
+        <v>2</v>
+      </c>
+      <c r="P86" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:16">
+      <c r="C87" s="2">
+        <v>319</v>
+      </c>
+      <c r="D87" s="2">
+        <v>2</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G87" s="2">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2">
+        <f t="shared" si="4"/>
+        <v>410</v>
+      </c>
+      <c r="I87" s="2">
+        <v>20</v>
+      </c>
+      <c r="J87" s="2">
+        <v>32</v>
+      </c>
+      <c r="K87" s="2">
+        <v>2</v>
+      </c>
+      <c r="L87" s="2">
+        <v>1</v>
+      </c>
+      <c r="M87" s="2">
+        <v>2</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O87" s="2">
+        <v>4</v>
+      </c>
+      <c r="P87" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:16">
+      <c r="C88" s="2">
+        <v>320</v>
+      </c>
+      <c r="D88" s="2">
+        <v>2</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G88" s="2">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2">
+        <f t="shared" si="4"/>
+        <v>410</v>
+      </c>
+      <c r="I88" s="2">
+        <v>20</v>
+      </c>
+      <c r="J88" s="2">
+        <v>2001</v>
+      </c>
+      <c r="K88" s="2">
+        <v>20</v>
+      </c>
+      <c r="L88" s="2">
+        <v>1</v>
+      </c>
+      <c r="M88" s="2">
+        <v>20</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O88" s="2">
+        <v>4</v>
+      </c>
+      <c r="P88" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:16">
+      <c r="C89" s="2">
+        <v>321</v>
+      </c>
+      <c r="D89" s="2">
+        <v>2</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G89" s="2">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2">
+        <f t="shared" si="4"/>
+        <v>410</v>
+      </c>
+      <c r="I89" s="2">
+        <v>20</v>
+      </c>
+      <c r="J89" s="2">
+        <v>31</v>
+      </c>
+      <c r="K89" s="2">
+        <v>2</v>
+      </c>
+      <c r="L89" s="2">
+        <v>1</v>
+      </c>
+      <c r="M89" s="2">
+        <v>2</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O89" s="2">
+        <v>4</v>
+      </c>
+      <c r="P89" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:16">
+      <c r="C90" s="2">
+        <v>322</v>
+      </c>
+      <c r="D90" s="2">
+        <v>2</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G90" s="2">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2">
+        <f t="shared" si="4"/>
+        <v>430</v>
+      </c>
+      <c r="I90" s="2">
+        <v>10</v>
+      </c>
+      <c r="J90" s="2">
+        <v>93</v>
+      </c>
+      <c r="K90" s="2">
+        <v>2</v>
+      </c>
+      <c r="L90" s="2">
+        <v>1</v>
+      </c>
+      <c r="M90" s="2">
+        <v>2</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O90" s="2">
+        <v>6</v>
+      </c>
+      <c r="P90" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:16">
+      <c r="C91" s="2">
+        <v>323</v>
+      </c>
+      <c r="D91" s="2">
+        <v>2</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G91" s="2">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2">
+        <f t="shared" si="4"/>
+        <v>430</v>
+      </c>
+      <c r="I91" s="2">
+        <v>10</v>
+      </c>
+      <c r="J91" s="2">
+        <v>91</v>
+      </c>
+      <c r="K91" s="2">
+        <v>2</v>
+      </c>
+      <c r="L91" s="2">
+        <v>1</v>
+      </c>
+      <c r="M91" s="2">
+        <v>2</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O91" s="2">
+        <v>6</v>
+      </c>
+      <c r="P91" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:16">
+      <c r="C92" s="2">
+        <v>324</v>
+      </c>
+      <c r="D92" s="2">
+        <v>2</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G92" s="2">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2">
+        <f t="shared" si="4"/>
+        <v>430</v>
+      </c>
+      <c r="I92" s="2">
+        <v>10</v>
+      </c>
+      <c r="J92" s="2">
+        <v>92</v>
+      </c>
+      <c r="K92" s="2">
+        <v>2</v>
+      </c>
+      <c r="L92" s="2">
+        <v>1</v>
+      </c>
+      <c r="M92" s="2">
+        <v>2</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O92" s="2">
+        <v>6</v>
+      </c>
+      <c r="P92" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:O5" errorStyle="warning">
